--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45826</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>45481</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45517</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>45201</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45356</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45965</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44986</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>44713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44960</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45488</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45826</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46100</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45805</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>44606</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>46051</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44501</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44987</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44861</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45016</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>46204</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45826</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44498</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44915</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45093</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45893</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>45443</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>45601</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>46204</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>46265</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44559</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45016</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45357</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45176</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45613</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45925</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45061</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>45960</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>45562</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45280</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>46038</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45601</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>46057</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>45463</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>45671</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45505</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45436</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44823</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>46139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>45208</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>45204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45936</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44970</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>45955</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>46006</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>44817</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>45568</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>46049</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45236</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>46090</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>46196</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44977</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>46258</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>46258</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>46258</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>46281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>46281</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>45826</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45839</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45021</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45735</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44727</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44519</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44615</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44776</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44808</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>44803</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>44851</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44847</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>44859</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44797</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44526</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44795</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44474</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44477</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44459</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44694</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>44585</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>44678</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44476</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44755</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44795</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44519</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44861</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44662</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44872</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44531</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44686</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44503</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44781</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44498</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44472</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44816</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>44704</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44704</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45735</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>44915</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45488</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45643</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45316</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>45106</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>45218</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45443</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>45114</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>45698</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44985</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45561</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45597</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45320</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>45517</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45559</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45099</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45147</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45092</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44761</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45036</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45035</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45611</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44516</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44698</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45071</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44935</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45120</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44592</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45635</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45104</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>45526</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45266</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44671</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45587</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>44687</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44922</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45479</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45481</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45177</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>45463</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45463</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>45148</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44984</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45443</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45266</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45679</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45770</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45329</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45329</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45637</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44943</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44739</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45505</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45677</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45369</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45103</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45576</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45005</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45705</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45174</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45121</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45481</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>45775</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44866</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45068</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45265</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45265</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45463</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45205</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45316</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44908</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45223</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45463</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45505</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45113</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45481</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44952</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45198</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44935</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45206</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45553</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45215</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>44952</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45562</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45105</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45889</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>45981</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44936</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45190</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>46136</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45476</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45149</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45077</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45068</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>45387</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45895</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45484</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45484</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45595</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45894</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45892</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45895</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45561</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45894</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45463</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45894</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45894</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44697</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45901</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45898</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>45903</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45903</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45443</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45909</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45488</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45867</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45911</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45911</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45665</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45911</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45214</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45915</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>44496</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45943</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45912</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45916</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>44971</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45103</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45182</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45919</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>45918</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45922</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>45923</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45923</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45774</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45538</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45925</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45481</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45908</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>45926</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45356</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>46142</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45523</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>46142</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45930</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45698</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45041</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>46142</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45329</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45932</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45932</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45937</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>45484</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45484</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45565</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45799</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45939</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45937</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45938</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>45937</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45939</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45939</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45937</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45478</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45938</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>46148</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>45944</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45944</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>46148</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>45944</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45112</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45944</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>45944</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45944</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45793</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45944</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45944</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45481</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45946</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45154</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45947</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>45947</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45198</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45950</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45951</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45329</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45953</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45953</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45952</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45955</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45756</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45954</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45955</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>46083</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45665</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>46153</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45645</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45471</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45719</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45561</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>46155</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45967</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45559</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45966</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45966</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45905</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>44524</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>46155</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45971</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45971</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>45968</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45968</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45546</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45566</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45762</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>45566</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45756</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45121</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45975</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45743</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45975</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45975</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45029</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45978</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45979</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>45980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46154</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>44980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45140</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45985</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45705</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>45985</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>45985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45077</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>44505</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46090</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45635</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>46160</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45986</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>44859</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45502</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45645</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45993</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45113</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>44551</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45479</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>46160</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44938</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>46160</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45775</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>45622</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33759,7 +33759,7 @@
         <v>45078</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45246</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>45604</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>46162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45995</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>46162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>45379</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45996</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>46001</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>46001</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>46093</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>46001</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45330</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45448</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45825</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45774</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>46164</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>46006</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45560</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45149</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>46169</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>46168</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45551</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45330</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45072</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45706</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45148</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>46168</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>46170</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44952</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45677</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45240</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45463</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45463</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45645</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45476</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>45944</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>45160</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>46035</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46036</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46174</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46174</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45589</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45443</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>46036</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45589</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45604</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45506</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>44826</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44781</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>46171</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>46171</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45316</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>46038</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45574</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45103</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>44894</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>46042</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45590</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45336</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45590</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>46045</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45194</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>46049</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>45684</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45646</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38943,7 +38943,7 @@
         <v>45113</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>46048</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>46051</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>46051</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>46051</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45174</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>46129</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45463</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>45593</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>46055</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>46057</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46056</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46056</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45113</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>46057</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46057</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>46178</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45246</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>45282</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45524</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>45524</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>44592</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40614,7 +40614,7 @@
         <v>44592</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40687,7 +40687,7 @@
         <v>46070</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>45518</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44992</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>46073</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>46073</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>46072</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45565</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>46078</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>46078</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>46078</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>46078</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>46078</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>46076</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>46078</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>46078</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46084</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>46185</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>46185</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>46086</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>46188</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>45154</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>46085</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45448</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>46185</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>46185</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>46185</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>46185</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>46185</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45485</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45093</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45545</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>44993</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45712</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>46092</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43284,7 +43284,7 @@
         <v>46094</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>46094</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>46093</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46093</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46093</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>46097</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>46191</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>46191</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>44879</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44774</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>46104</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45619</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>45387</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>46195</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>46197</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45428</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>46107</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>46198</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45756</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45645</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>46244</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>46201</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>46202</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>45748</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>45492</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>46202</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45705</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>46113</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46202</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45378</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45357</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45566</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>46119</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45545</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45576</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45329</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45526</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46201</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46202</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>46244</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>46201</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45476</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>46244</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45560</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>46202</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>46202</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>46202</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45392</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>46128</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>46199</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45329</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>46202</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>46129</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>46129</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>46129</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>46112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>44988</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>44988</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>46129</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>46202</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>46112</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>46128</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48050,7 +48050,7 @@
         <v>46199</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>46132</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>46132</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>46204</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45239</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46132</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>46132</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>45099</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>46205</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>45104</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45104</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45774</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>46205</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>46204</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>46204</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>46204</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>46205</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>45113</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>46205</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>46136</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>45329</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>45174</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>46205</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>46205</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45092</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>46247</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45560</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45481</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>46246</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>46204</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>44936</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>44888</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>46248</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>46251</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45014</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>46209</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>46248</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>46248</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50997,7 +50997,7 @@
         <v>46206</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>46248</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45590</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>46208</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>46206</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>44925</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46208</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51533,7 +51533,7 @@
         <v>46248</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46205</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>46206</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45189</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>45282</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>44953</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>46251</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>46248</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>46248</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52225,7 +52225,7 @@
         <v>46205</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52303,7 +52303,7 @@
         <v>46205</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>46206</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>44908</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>46253</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>45187</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>46209</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>45481</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>45505</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>45114</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46252</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45098</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53146,7 +53146,7 @@
         <v>46209</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>46253</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>46255</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>46211</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         <v>46211</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>46254</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45712</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45167</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>46254</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>46255</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53901,7 +53901,7 @@
         <v>45576</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>46211</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>46212</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>46255</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>46211</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46254</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45534</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>46214</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>45484</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>46258</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>46258</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>46258</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54837,7 +54837,7 @@
         <v>46258</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>46258</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>46258</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>44952</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>46258</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>46259</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55300,7 +55300,7 @@
         <v>46259</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>46258</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>46258</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>46259</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         <v>46259</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>46258</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45313</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45341</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45622</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>46216</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>45316</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56143,7 +56143,7 @@
         <v>46217</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56216,7 +56216,7 @@
         <v>46261</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56294,7 +56294,7 @@
         <v>46218</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>46260</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56445,7 +56445,7 @@
         <v>45610</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>46220</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>44888</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>46262</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>46262</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45560</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56908,7 +56908,7 @@
         <v>46262</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>45313</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45774</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45774</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>46001</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45282</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>46262</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>46265</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45666</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45272</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>46267</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>45735</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57814,7 +57814,7 @@
         <v>46267</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>46267</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45099</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>46267</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58121,7 +58121,7 @@
         <v>46267</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>46267</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58277,7 +58277,7 @@
         <v>44817</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58355,7 +58355,7 @@
         <v>46267</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>45266</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>46226</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58589,7 +58589,7 @@
         <v>46269</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>46226</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58745,7 +58745,7 @@
         <v>45734</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>46268</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>46268</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>46268</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>46226</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>46226</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>46268</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>46226</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>46269</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46268</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>46268</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>44988</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45599</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>46273</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>46272</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>46272</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>46273</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>46273</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>46272</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>46232</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>46275</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>46275</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60441,7 +60441,7 @@
         <v>46281</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>46281</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>46281</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>46281</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>46281</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>46281</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60909,7 +60909,7 @@
         <v>46280</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60987,7 +60987,7 @@
         <v>46281</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>46281</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61143,7 +61143,7 @@
         <v>45791</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61221,7 +61221,7 @@
         <v>46281</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>46281</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61377,7 +61377,7 @@
         <v>46282</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61455,7 +61455,7 @@
         <v>46282</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61533,7 +61533,7 @@
         <v>46239</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>45750</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>46240</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61757,7 +61757,7 @@
         <v>46240</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61835,7 +61835,7 @@
         <v>46282</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61913,7 +61913,7 @@
         <v>45799</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45800</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>46282</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62147,7 +62147,7 @@
         <v>45800</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62225,7 +62225,7 @@
         <v>45805</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62303,7 +62303,7 @@
         <v>44595</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62376,7 +62376,7 @@
         <v>45805</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>45805</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62532,7 +62532,7 @@
         <v>45813</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>45541</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62688,7 +62688,7 @@
         <v>45817</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>45814</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62839,7 +62839,7 @@
         <v>45814</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45826</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62990,7 +62990,7 @@
         <v>45826</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>45826</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63146,7 +63146,7 @@
         <v>45826</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63224,7 +63224,7 @@
         <v>45826</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63302,7 +63302,7 @@
         <v>45826</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63380,7 +63380,7 @@
         <v>45826</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         <v>45831</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63531,7 +63531,7 @@
         <v>45833</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63609,7 +63609,7 @@
         <v>45832</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63682,7 +63682,7 @@
         <v>45832</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63755,7 +63755,7 @@
         <v>45833</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
         <v>45832</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45832</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63979,7 +63979,7 @@
         <v>45835</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>45838</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64135,7 +64135,7 @@
         <v>45839</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64213,7 +64213,7 @@
         <v>45839</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>44845</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64369,7 +64369,7 @@
         <v>45849</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>45848</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64520,7 +64520,7 @@
         <v>45848</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45849</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64671,7 +64671,7 @@
         <v>45849</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45854</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>45856</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>45856</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64978,7 +64978,7 @@
         <v>45867</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45867</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45867</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65212,7 +65212,7 @@
         <v>45867</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65290,7 +65290,7 @@
         <v>45868</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65368,7 +65368,7 @@
         <v>45868</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>45868</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65524,7 +65524,7 @@
         <v>45870</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65602,7 +65602,7 @@
         <v>45882</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45883</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45882</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65826,7 +65826,7 @@
         <v>45882</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65899,7 +65899,7 @@
         <v>45883</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65977,7 +65977,7 @@
         <v>44607</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66055,7 +66055,7 @@
         <v>45020</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66133,7 +66133,7 @@
         <v>44638</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66211,7 +66211,7 @@
         <v>45386</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>45638</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66367,7 +66367,7 @@
         <v>45250</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>45021</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66523,7 +66523,7 @@
         <v>44943</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66601,7 +66601,7 @@
         <v>45755</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66674,7 +66674,7 @@
         <v>45834</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66752,7 +66752,7 @@
         <v>45755</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66825,7 +66825,7 @@
         <v>46168</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66898,7 +66898,7 @@
         <v>46247</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45826</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>45481</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45201</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45356</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>44986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>44713</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44960</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45488</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45826</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44606</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>46051</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45915</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45826</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>44861</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44987</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45016</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>44498</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45443</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45893</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45093</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>46204</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>46265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>44915</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45463</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45436</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45505</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45176</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>46038</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45601</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>46057</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45016</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>45613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46188</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45280</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45562</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45061</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45357</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44823</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45568</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45811</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>46006</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45236</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45826</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44977</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45839</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45204</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>46196</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45208</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>46258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>46281</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46281</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>46090</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>46290</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45735</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>44727</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44519</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44615</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44808</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44803</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>44851</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44859</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44795</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44526</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44474</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44477</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44476</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44694</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44585</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44678</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>44476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44755</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44795</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44519</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44861</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>44662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44686</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44781</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44498</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44472</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44816</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>44711</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>44704</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>44704</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45329</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45329</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45206</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45378</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44866</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45619</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45068</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45369</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45336</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45734</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45428</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45463</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45392</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44953</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45092</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45463</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44908</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45551</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45443</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45526</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45154</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45135</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45484</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45443</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45174</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45481</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45944</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45479</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45476</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45476</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>46036</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>46035</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>44980</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45589</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45589</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>44935</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45604</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45481</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>46038</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45889</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45894</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45892</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>46042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45895</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45895</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45800</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45590</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45590</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45901</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45800</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45901</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45518</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>46045</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45646</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>46049</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>45566</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45903</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44915</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44985</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44992</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>46051</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>46051</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45799</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>44888</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45909</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>46056</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>46055</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45481</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>46056</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45912</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>46057</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45911</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46057</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45918</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44952</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45919</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45922</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>45923</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45114</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>46070</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44592</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44592</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45923</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45926</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>46072</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44524</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46073</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>46073</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45194</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45565</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46076</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45706</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>46078</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>46078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>46078</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45930</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>46078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45553</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45320</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>46078</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>46078</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44936</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44592</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>46078</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45805</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>46085</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45805</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45595</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45587</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45932</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46084</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45932</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>46086</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45937</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45938</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45938</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45799</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45937</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45937</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>46093</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>46093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45448</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45939</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45939</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>46094</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45448</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45944</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45944</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45944</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45705</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45944</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45705</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45944</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>46097</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45944</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45944</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45218</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45541</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45793</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45950</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45947</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45947</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>46104</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45952</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45463</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46107</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45951</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44952</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45953</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45559</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45953</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45559</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45954</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45955</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44697</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45955</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45005</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>46113</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>46119</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45099</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44817</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45481</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45966</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45966</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45968</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45479</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>46112</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45967</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>44971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45666</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45814</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45814</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45813</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>46112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45973</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46128</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>46129</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46132</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45014</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46129</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>46132</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45975</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45817</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45112</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46129</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46129</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45975</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>46132</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45978</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45980</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46132</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46128</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45979</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45565</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45981</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45114</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45985</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45985</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45985</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45986</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45985</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45113</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45665</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46136</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45993</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45995</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45996</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45140</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45908</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>46001</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45103</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46001</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45174</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>46001</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45775</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45943</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46006</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45748</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45484</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45867</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45774</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>45981</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>45093</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45698</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45826</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45826</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45826</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45826</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44988</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>44988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45566</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46142</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45826</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45826</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44496</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46142</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45523</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45481</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45735</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45077</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>46142</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45524</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45524</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45832</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45068</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45832</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45832</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45831</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45832</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45833</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45833</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45905</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45966</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>46154</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46083</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45835</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46155</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>45149</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45838</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46155</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44943</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46160</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45341</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>45756</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45502</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45379</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>46160</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45635</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>45604</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45645</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>46162</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45561</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45679</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45839</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45839</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45104</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45538</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>45182</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45113</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>46090</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44845</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45121</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>44505</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45272</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>46162</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45756</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>46164</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45104</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45104</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45848</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45848</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45849</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45849</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46093</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45825</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45849</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45854</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>46168</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45856</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39252,7 +39252,7 @@
         <v>45099</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45856</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>46169</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44894</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45488</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>46171</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>46171</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46174</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46174</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45545</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>46129</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45867</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45868</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45867</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45560</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45560</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45867</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45868</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45868</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45867</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45121</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45870</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>46178</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44971</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45562</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45756</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45593</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>46185</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>46185</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46185</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46185</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45712</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>46185</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>46185</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45113</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>46188</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45622</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>45443</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>45484</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45484</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45698</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45775</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45120</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46191</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>46191</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>45560</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45330</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>46195</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45329</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>45712</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45476</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45036</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45035</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>44551</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45426</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>46197</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45665</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>46201</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46199</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>46201</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>46201</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45190</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>46199</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>46198</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>46202</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45099</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>46202</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45506</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>46202</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>46202</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45485</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>46202</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>46202</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>46202</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>46202</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>45622</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>46202</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45316</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45883</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46204</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46204</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>46204</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>46204</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>46205</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>46205</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>46205</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>46205</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>46204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>46205</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>46205</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>46205</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>46205</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>46204</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>46205</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45597</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>46209</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>45517</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46980,7 +46980,7 @@
         <v>46206</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>45645</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>46206</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45643</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45645</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>46206</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>46251</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>46208</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45177</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45106</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>46208</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>46209</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46252</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>46209</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>46251</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>46211</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>46211</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45770</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>45214</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45098</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45677</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>46211</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>46254</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>46253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48812,7 +48812,7 @@
         <v>45240</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>46253</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>46254</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>46211</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>46212</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45149</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>46258</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45147</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>46254</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>46258</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         <v>44698</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>46255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46258</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>46255</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>46258</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>46214</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>46255</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45774</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45774</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46258</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>46258</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45561</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46258</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46258</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>46259</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>46218</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45103</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45103</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45189</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45239</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>46259</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45160</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>46217</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>46260</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>46259</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>46259</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45187</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45174</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>44774</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>46262</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>46261</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>46262</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>44761</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>44687</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>46216</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>46262</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>46262</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52574,7 +52574,7 @@
         <v>45637</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45198</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52725,7 +52725,7 @@
         <v>44671</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>44826</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>45265</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>46220</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53032,7 +53032,7 @@
         <v>45743</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45719</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45313</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>46268</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>45266</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45266</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53573,7 +53573,7 @@
         <v>46268</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46268</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>46267</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>46267</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53963,7 +53963,7 @@
         <v>46268</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>46267</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>46268</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>46267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>46267</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>46267</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>46269</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45357</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45484</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46226</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>46226</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>46226</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54899,7 +54899,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54972,7 +54972,7 @@
         <v>45282</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55045,7 +55045,7 @@
         <v>46226</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55123,7 +55123,7 @@
         <v>46226</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55201,7 +55201,7 @@
         <v>44781</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>46269</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>46272</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>44922</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55508,7 +55508,7 @@
         <v>46272</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45463</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>45463</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>46273</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>46273</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>46273</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>46275</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>46232</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>46275</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45246</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45282</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56356,7 +56356,7 @@
         <v>45215</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56434,7 +56434,7 @@
         <v>46280</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>45677</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>44879</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56658,7 +56658,7 @@
         <v>45485</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56731,7 +56731,7 @@
         <v>45645</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>46281</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56882,7 +56882,7 @@
         <v>46282</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>46239</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57033,7 +57033,7 @@
         <v>46282</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>46281</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>46281</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         <v>46281</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57345,7 +57345,7 @@
         <v>46282</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>45316</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>45316</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>46281</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>46281</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>46281</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57803,7 +57803,7 @@
         <v>46281</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>46281</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45574</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58037,7 +58037,7 @@
         <v>46282</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45526</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58193,7 +58193,7 @@
         <v>45481</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58271,7 +58271,7 @@
         <v>46286</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46240</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45329</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>46240</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45546</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>44925</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>44952</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>45387</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45387</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45735</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>44935</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45882</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>46244</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>46288</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45576</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45561</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>45266</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>46265</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>46244</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>46244</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>44993</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59879,7 +59879,7 @@
         <v>46288</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>46281</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>46248</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60108,7 +60108,7 @@
         <v>46248</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>46290</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>46290</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45882</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>46290</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60483,7 +60483,7 @@
         <v>45072</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>46248</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60639,7 +60639,7 @@
         <v>45078</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>46290</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60795,7 +60795,7 @@
         <v>46289</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>46290</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>46246</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>46248</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>46289</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>45189</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>46247</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>46248</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61482,7 +61482,7 @@
         <v>46248</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>45894</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>45774</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61706,7 +61706,7 @@
         <v>46248</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46290</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>46290</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>45105</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45167</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45635</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45113</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>45356</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62320,7 +62320,7 @@
         <v>44516</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62398,7 +62398,7 @@
         <v>45505</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45329</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>45329</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62632,7 +62632,7 @@
         <v>44952</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62705,7 +62705,7 @@
         <v>45148</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62778,7 +62778,7 @@
         <v>45488</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62851,7 +62851,7 @@
         <v>45610</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62929,7 +62929,7 @@
         <v>45505</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>44859</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         <v>45774</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         <v>45471</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45481</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>45684</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45077</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45329</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63533,7 +63533,7 @@
         <v>45265</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45590</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45246</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>45092</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63840,7 +63840,7 @@
         <v>45071</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>45611</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45492</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64069,7 +64069,7 @@
         <v>45148</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64142,7 +64142,7 @@
         <v>45534</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64220,7 +64220,7 @@
         <v>45566</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64298,7 +64298,7 @@
         <v>45560</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64376,7 +64376,7 @@
         <v>45705</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64454,7 +64454,7 @@
         <v>45330</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64527,7 +64527,7 @@
         <v>45505</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45282</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64678,7 +64678,7 @@
         <v>44739</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64751,7 +64751,7 @@
         <v>45576</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64829,7 +64829,7 @@
         <v>45463</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64907,7 +64907,7 @@
         <v>45113</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64980,7 +64980,7 @@
         <v>44938</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65058,7 +65058,7 @@
         <v>45576</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>45463</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65214,7 +65214,7 @@
         <v>45313</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65292,7 +65292,7 @@
         <v>45154</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65370,7 +65370,7 @@
         <v>45599</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65443,7 +65443,7 @@
         <v>44988</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>45791</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65599,7 +65599,7 @@
         <v>44607</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65677,7 +65677,7 @@
         <v>44638</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65755,7 +65755,7 @@
         <v>45020</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65833,7 +65833,7 @@
         <v>45386</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>45638</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>45250</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66067,7 +66067,7 @@
         <v>45021</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>44943</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66223,7 +66223,7 @@
         <v>45755</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45834</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66374,7 +66374,7 @@
         <v>45755</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66447,7 +66447,7 @@
         <v>46168</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66520,7 +66520,7 @@
         <v>46247</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45826</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>45481</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45201</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45356</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>45965</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>44986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>44713</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>44960</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>45488</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45826</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44606</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>46051</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>45915</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45826</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>44861</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44987</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45016</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>44498</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>44694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45443</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45893</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45093</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>46204</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>46265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>44915</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45463</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45436</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45505</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45176</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>46038</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45601</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>46057</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45016</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>45613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46188</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45280</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45562</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45061</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>45357</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44823</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44970</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>45568</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45811</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>46006</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45236</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45826</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44977</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45839</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45204</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>46196</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45208</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>46258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>46281</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46281</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>46090</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>46290</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>45021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45735</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>44727</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44519</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44615</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44776</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44808</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44803</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>44851</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44859</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44797</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44795</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44526</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44474</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44477</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44476</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44694</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44585</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44678</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>44476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44755</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44795</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44519</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44861</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>44662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44686</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44503</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44781</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44498</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44472</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44816</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>44711</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>44704</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>44704</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45329</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45329</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45206</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45378</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44866</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45619</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45068</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45369</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45336</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45734</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45428</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45463</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45392</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44953</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45092</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45463</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44908</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>45551</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45443</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45526</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45154</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45135</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45484</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45443</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45174</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45481</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45944</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45479</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45476</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45476</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>46036</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>46035</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>44980</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45589</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45589</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>44935</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45604</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45481</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>46038</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45889</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45894</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45892</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>46042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45895</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45895</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45800</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45590</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45590</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45898</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45901</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45800</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45901</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45518</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>46045</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45646</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>46049</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>45566</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45903</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44915</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44985</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44992</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>46051</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>46051</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45799</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>44888</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45909</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>46056</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>46055</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45481</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>46056</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45912</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>46057</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45911</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46057</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45918</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44952</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45919</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45922</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>45923</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45114</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>46070</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44592</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44592</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45923</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45926</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>46072</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44524</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46073</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>46073</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45194</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45565</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46076</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>45706</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>46078</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>46078</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>46078</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45930</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>46078</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45553</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45320</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>46078</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>46078</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44936</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>44592</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>46078</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45805</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>46085</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45805</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45595</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45587</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45932</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46084</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45932</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>46086</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45937</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45938</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45938</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45799</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45937</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45937</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>46093</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>46093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45448</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45939</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45939</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>46094</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45944</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45448</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45944</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45944</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45944</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45705</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45944</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45705</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45944</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>46097</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45944</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45944</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45218</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45541</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45946</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45793</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45950</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45947</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45947</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>46104</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45952</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45463</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46107</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45951</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44952</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45953</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45559</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45953</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45559</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45954</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45955</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44697</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45955</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45005</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>46113</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>46119</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45099</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44817</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45481</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45966</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45966</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45968</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45479</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>46112</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45967</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>44971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45666</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45814</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45814</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45813</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>46112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45973</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46128</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>46129</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46132</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45014</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46129</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>46132</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45975</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45817</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45112</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46129</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46129</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45975</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>46132</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45978</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45980</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46132</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46128</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45979</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45565</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45981</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45114</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45985</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45985</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45985</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45986</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>45985</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45113</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45665</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46136</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45993</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45995</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45996</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45029</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45140</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45908</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>46001</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45103</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46001</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45174</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>46001</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45775</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45943</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46006</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45748</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45484</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45867</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45774</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>45981</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>45093</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45698</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45826</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45826</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45826</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45826</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44988</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>44988</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45566</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46142</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45826</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45826</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44496</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46142</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45523</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45481</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45735</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45077</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>46142</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45524</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45524</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45832</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45068</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45832</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46148</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45832</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45831</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45832</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45833</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45833</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45905</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45966</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>46154</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46083</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45835</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46155</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>45149</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45838</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46155</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44943</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46160</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45341</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>45756</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45502</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45379</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>46160</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45635</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>45604</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45645</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>46162</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45561</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45679</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45839</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45839</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45104</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45538</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>45182</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45113</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>46090</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44845</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45121</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>44505</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45272</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>46162</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45756</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>46164</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45104</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45104</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45848</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45848</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45849</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45849</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46093</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45825</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45849</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45854</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>46168</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45856</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39252,7 +39252,7 @@
         <v>45099</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45856</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>46169</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44894</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45488</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>46171</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>46171</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46174</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46174</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45545</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>46129</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45867</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45868</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45867</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45560</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45560</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45867</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45868</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45868</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45867</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45121</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>45870</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>46178</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44971</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45562</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45756</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45593</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>46185</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>46185</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46185</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46185</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45712</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>46185</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>46185</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>45041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45113</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>46188</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45622</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>45443</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>45484</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45484</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45698</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45775</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45120</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46191</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>46191</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>45560</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45330</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>46195</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45329</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>45712</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45476</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45036</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45035</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>44551</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45426</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>46197</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45665</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>46201</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46199</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>46201</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>46201</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45190</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>46199</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>46198</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>46202</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45099</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>46202</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45506</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>46202</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>46202</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         <v>45485</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>46202</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>46202</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>46202</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>46202</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>45622</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>46202</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45316</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45883</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46204</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46204</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>46204</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>46204</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>46205</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>46205</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>46205</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>46205</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>46204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>46205</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>46205</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>46205</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>46205</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>46204</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>46205</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>45597</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>46209</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>45517</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46980,7 +46980,7 @@
         <v>46206</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>45645</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>46206</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45643</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45645</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>46206</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>46251</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>46208</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45177</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45106</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>46208</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>46209</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46252</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>46209</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>46251</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>46211</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>46211</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45770</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>45214</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45098</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45677</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>46211</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>46254</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>46253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48812,7 +48812,7 @@
         <v>45240</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>46253</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>46254</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>46211</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>46212</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45149</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>46258</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45147</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>46254</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>46258</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         <v>44698</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>46255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46258</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>46255</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>46258</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>46214</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>46255</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45774</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45774</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46258</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>46258</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45561</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46258</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46258</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>46259</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>46218</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45103</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45103</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45189</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45239</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>46259</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45160</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>46217</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>46260</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>46259</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>46259</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>45187</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45174</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>44774</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>46262</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>46261</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>46262</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>44761</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>44687</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>46216</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>46262</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>46262</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52574,7 +52574,7 @@
         <v>45637</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45198</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52725,7 +52725,7 @@
         <v>44671</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>44826</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>45265</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>46220</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53032,7 +53032,7 @@
         <v>45743</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45719</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45313</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>46268</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>45266</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45266</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53573,7 +53573,7 @@
         <v>46268</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46268</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>46267</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>46267</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53963,7 +53963,7 @@
         <v>46268</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>46267</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>46268</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>46267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>46267</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>46267</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>46269</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45357</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45484</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46226</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>46226</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>46226</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54899,7 +54899,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54972,7 +54972,7 @@
         <v>45282</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55045,7 +55045,7 @@
         <v>46226</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55123,7 +55123,7 @@
         <v>46226</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55201,7 +55201,7 @@
         <v>44781</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>46269</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>46272</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>44922</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55508,7 +55508,7 @@
         <v>46272</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45463</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>45463</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>46273</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>46273</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>46273</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>46275</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>46232</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>46275</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45246</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45282</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56356,7 +56356,7 @@
         <v>45215</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56434,7 +56434,7 @@
         <v>46280</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>45677</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>44879</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56658,7 +56658,7 @@
         <v>45485</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56731,7 +56731,7 @@
         <v>45645</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>46281</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56882,7 +56882,7 @@
         <v>46282</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>46239</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57033,7 +57033,7 @@
         <v>46282</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>46281</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>46281</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         <v>46281</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57345,7 +57345,7 @@
         <v>46282</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>45316</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>45316</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>46281</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>46281</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>46281</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57803,7 +57803,7 @@
         <v>46281</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>46281</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45574</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58037,7 +58037,7 @@
         <v>46282</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45526</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58193,7 +58193,7 @@
         <v>45481</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58271,7 +58271,7 @@
         <v>46286</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46240</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45329</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>46240</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45546</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>44925</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>44952</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>45387</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45387</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45735</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>44935</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45882</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>46244</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>46288</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45576</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45561</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>45266</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>46265</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>46244</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>46244</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>44993</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59879,7 +59879,7 @@
         <v>46288</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59952,7 +59952,7 @@
         <v>46281</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>46248</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60108,7 +60108,7 @@
         <v>46248</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>46290</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>46290</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45882</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>46290</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60483,7 +60483,7 @@
         <v>45072</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>46248</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60639,7 +60639,7 @@
         <v>45078</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>46290</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60795,7 +60795,7 @@
         <v>46289</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>46290</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>46246</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>46248</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>46289</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>45189</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>46247</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>46248</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61482,7 +61482,7 @@
         <v>46248</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>45894</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>45774</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61706,7 +61706,7 @@
         <v>46248</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>46290</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>46290</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>45105</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>45167</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45635</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45113</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>45356</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62320,7 +62320,7 @@
         <v>44516</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62398,7 +62398,7 @@
         <v>45505</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45329</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>45329</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62632,7 +62632,7 @@
         <v>44952</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62705,7 +62705,7 @@
         <v>45148</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62778,7 +62778,7 @@
         <v>45488</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62851,7 +62851,7 @@
         <v>45610</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62929,7 +62929,7 @@
         <v>45505</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>44859</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         <v>45774</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         <v>45471</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45481</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>45684</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45077</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45329</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63533,7 +63533,7 @@
         <v>45265</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45590</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45246</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>45092</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63840,7 +63840,7 @@
         <v>45071</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>45611</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45492</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64069,7 +64069,7 @@
         <v>45148</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64142,7 +64142,7 @@
         <v>45534</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64220,7 +64220,7 @@
         <v>45566</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64298,7 +64298,7 @@
         <v>45560</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64376,7 +64376,7 @@
         <v>45705</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64454,7 +64454,7 @@
         <v>45330</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64527,7 +64527,7 @@
         <v>45505</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45282</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64678,7 +64678,7 @@
         <v>44739</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64751,7 +64751,7 @@
         <v>45576</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64829,7 +64829,7 @@
         <v>45463</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64907,7 +64907,7 @@
         <v>45113</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64980,7 +64980,7 @@
         <v>44938</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65058,7 +65058,7 @@
         <v>45576</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>45463</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65214,7 +65214,7 @@
         <v>45313</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65292,7 +65292,7 @@
         <v>45154</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65370,7 +65370,7 @@
         <v>45599</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65443,7 +65443,7 @@
         <v>44988</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>45791</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65599,7 +65599,7 @@
         <v>44607</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65677,7 +65677,7 @@
         <v>44638</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65755,7 +65755,7 @@
         <v>45020</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65833,7 +65833,7 @@
         <v>45386</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>45638</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>45250</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66067,7 +66067,7 @@
         <v>45021</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>44943</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66223,7 +66223,7 @@
         <v>45755</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45834</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66374,7 +66374,7 @@
         <v>45755</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66447,7 +66447,7 @@
         <v>46168</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66520,7 +66520,7 @@
         <v>46247</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45488</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45826</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45805</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>46100</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>44606</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>46051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44501</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44987</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45915</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45826</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44861</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45016</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>46204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>44498</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44694</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44915</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45893</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45601</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45093</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45443</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>46205</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46204</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>46265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44960</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44559</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45016</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>46038</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45601</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45436</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>46057</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45960</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45357</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45613</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45176</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45061</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>45562</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>46188</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>45280</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>45463</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45671</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45505</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44823</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>46006</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45568</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45936</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45839</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45208</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45204</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44970</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>46281</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>46281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>46090</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>46295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46297</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45021</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>45735</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44727</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>44519</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44615</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44808</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44803</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>44851</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>44859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44795</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44526</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44474</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44477</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44476</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44694</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44585</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44678</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44476</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44795</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44519</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44861</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44662</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44686</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44781</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44498</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44472</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44816</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44711</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>44704</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>44704</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45735</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>44915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45488</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45643</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45218</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45316</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45443</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>45106</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45114</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45698</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44985</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45561</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44761</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45036</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45035</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>46001</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45320</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45597</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45099</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45147</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45559</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45092</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45611</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>44516</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>44698</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44935</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45476</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45892</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45895</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45071</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45894</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45791</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45894</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45895</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45635</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45104</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45120</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44592</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45901</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45898</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45944</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>46035</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45903</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>45903</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45266</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45903</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45426</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>46036</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45589</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>46036</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45589</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45604</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44671</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>46038</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46042</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45750</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45590</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45915</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45590</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46045</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45912</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>46049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45587</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45646</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45916</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>46051</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45799</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>44687</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45800</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>46051</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>46051</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45800</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45805</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45919</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44595</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45805</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45918</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>44922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45923</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45479</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>46055</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45481</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>46057</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45148</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>46056</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>46056</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>46057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>46057</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45485</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45463</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45926</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45177</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45930</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45443</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45932</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45329</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45329</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44984</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45266</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45679</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45770</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45932</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>44592</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44592</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>45637</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45937</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45799</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>46070</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45938</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45939</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45939</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45938</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45938</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>46073</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>46072</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46078</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46078</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45944</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45944</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45944</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>46078</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45944</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45944</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46078</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>44943</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45944</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44739</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45793</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45944</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45944</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45677</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45947</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45505</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>46078</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>46078</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45947</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45369</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45951</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45953</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45103</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45813</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45952</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45955</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>46086</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45954</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45955</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46085</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45576</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45705</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45541</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45481</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45005</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45775</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>44866</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45265</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>45121</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>46094</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45068</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45463</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45967</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45205</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>45966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46093</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>46093</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45817</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45966</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45316</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45973</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45975</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45223</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>46104</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44908</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45975</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45814</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45814</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45975</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45463</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45979</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45505</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45981</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45113</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46107</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45985</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44952</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45985</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>46113</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45481</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45986</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46119</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45198</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44935</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>45993</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45826</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45553</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45215</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>44952</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45826</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45995</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45562</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>46128</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>46129</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45826</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>46129</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46129</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45996</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46112</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45826</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>46129</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>46001</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45826</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>46112</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>46128</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>46001</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>46132</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>46132</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>45831</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>46132</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>46132</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45105</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45833</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45832</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44936</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45832</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>45190</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45833</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45832</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45077</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45068</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45387</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45484</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45484</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45835</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45113</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45595</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45561</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>46136</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45463</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45839</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45839</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>44697</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44845</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45443</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>45488</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>45849</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45848</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45848</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45849</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45849</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45665</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45214</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>45981</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35738,7 +35738,7 @@
         <v>44971</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>46136</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45103</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45182</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45854</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45856</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45774</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45538</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45856</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45481</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45356</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45523</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45698</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>45041</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>45329</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45867</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45867</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45484</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45484</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45565</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>45867</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44496</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45943</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45867</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>45867</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45868</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37726,7 +37726,7 @@
         <v>45868</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45868</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45112</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>45481</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>45154</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46142</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46142</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45198</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>46142</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>45329</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45756</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46148</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>46148</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45870</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45665</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>46083</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45645</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45471</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45905</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45719</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45966</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>46155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>45561</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45559</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46154</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44524</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46090</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45635</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45502</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45645</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45546</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45566</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45566</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45756</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45121</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46160</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46160</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45743</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45604</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45029</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>46162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>46162</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46093</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>45825</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>46164</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44980</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45140</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45705</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41551,7 +41551,7 @@
         <v>46169</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45077</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>44505</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44859</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>46174</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>46174</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>46171</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>46171</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>45883</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45883</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>45113</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>44551</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>46129</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45479</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>44938</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>46178</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45775</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45622</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45078</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45246</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>45189</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45379</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46185</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>46185</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>46188</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>46185</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>46185</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>46185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>46185</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46185</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45330</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>45448</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45774</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45560</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>46191</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>46191</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45149</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45551</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>46195</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45330</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45072</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45706</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46197</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45148</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46198</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>46201</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>46202</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>44952</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>46202</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>45135</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46202</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>46201</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>46202</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>46201</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>46202</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>46202</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>46202</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>46199</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>46202</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46202</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46199</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46204</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>46204</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45677</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45240</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>46205</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>46205</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>46204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>46204</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>46204</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46205</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46205</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45463</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45463</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46205</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46205</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45645</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46204</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>46209</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45476</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45160</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46208</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>46206</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>46208</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>46205</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>46206</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45443</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48358,7 +48358,7 @@
         <v>46205</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>46205</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>45506</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>46206</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>44826</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48743,7 +48743,7 @@
         <v>46209</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>44781</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45316</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>46209</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>46211</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45574</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>46211</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45103</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>44894</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>46212</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>46211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>46214</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45336</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>46258</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>46258</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>46258</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>46258</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>46258</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>46258</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45194</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45684</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>46259</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>46259</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>46258</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45113</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>46258</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46259</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>46259</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>46258</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>46216</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46217</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>46261</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45463</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>46218</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45593</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46260</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46220</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>46262</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46262</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45113</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46262</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45246</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46262</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45282</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>46267</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52359,7 +52359,7 @@
         <v>46267</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45524</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45524</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>46267</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>46267</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>46267</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46267</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>46267</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>46226</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>46269</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>46226</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45518</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53290,7 +53290,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>46268</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53446,7 +53446,7 @@
         <v>46268</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53524,7 +53524,7 @@
         <v>46226</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>46226</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>46268</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>46226</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>44992</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         <v>46269</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46268</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>46268</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45565</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54221,7 +54221,7 @@
         <v>46273</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>46272</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>46273</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>46273</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>46272</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>46232</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>46275</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>46275</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45154</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54986,7 +54986,7 @@
         <v>46281</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>46281</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>45448</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>46281</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45485</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>46281</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>46281</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55527,7 +55527,7 @@
         <v>46280</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>45093</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>46281</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>46281</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45545</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46281</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>46281</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>44993</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>46282</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>46282</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45712</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>46239</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>46240</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56536,7 +56536,7 @@
         <v>46240</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56614,7 +56614,7 @@
         <v>44879</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>44774</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         <v>46282</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>46282</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>45882</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45619</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45387</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>46244</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>45428</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>46244</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>46286</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45756</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45645</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45748</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57681,7 +57681,7 @@
         <v>45492</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45705</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>45378</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>46289</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45357</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58066,7 +58066,7 @@
         <v>45566</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>46246</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>46265</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>46288</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>45545</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45576</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>46288</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45329</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58675,7 +58675,7 @@
         <v>46289</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>45526</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>46248</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58909,7 +58909,7 @@
         <v>45476</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>46290</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>46290</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>46290</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59211,7 +59211,7 @@
         <v>46248</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>45560</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>46248</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45882</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59518,7 +59518,7 @@
         <v>45894</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45392</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59669,7 +59669,7 @@
         <v>45329</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46290</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>46293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>44988</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>44988</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>46247</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>46248</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>46290</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>46290</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>46290</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45239</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>46293</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60585,7 +60585,7 @@
         <v>46248</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60663,7 +60663,7 @@
         <v>46248</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60741,7 +60741,7 @@
         <v>45099</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>46293</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60897,7 +60897,7 @@
         <v>46248</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>46252</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>46295</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61209,7 +61209,7 @@
         <v>45104</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61282,7 +61282,7 @@
         <v>45104</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45774</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61428,7 +61428,7 @@
         <v>46295</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>46251</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>46295</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>46295</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45113</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>46295</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45329</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61964,7 +61964,7 @@
         <v>46251</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62042,7 +62042,7 @@
         <v>46281</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62120,7 +62120,7 @@
         <v>45174</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62198,7 +62198,7 @@
         <v>46294</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>45092</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45560</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46297</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45481</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>46297</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>46255</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>46253</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62817,7 +62817,7 @@
         <v>44936</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>46297</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62968,7 +62968,7 @@
         <v>44888</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>46254</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>45014</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>46297</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63270,7 +63270,7 @@
         <v>46244</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63348,7 +63348,7 @@
         <v>46254</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63426,7 +63426,7 @@
         <v>46297</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63504,7 +63504,7 @@
         <v>45590</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>46297</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>46255</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63733,7 +63733,7 @@
         <v>44925</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>46211</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>46253</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>46297</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>46254</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>46255</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45189</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45282</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>44953</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64420,7 +64420,7 @@
         <v>44908</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45187</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45481</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>45505</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         <v>45114</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64800,7 +64800,7 @@
         <v>45098</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64878,7 +64878,7 @@
         <v>45712</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64956,7 +64956,7 @@
         <v>45167</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>45576</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65107,7 +65107,7 @@
         <v>45534</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65185,7 +65185,7 @@
         <v>45484</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65263,7 +65263,7 @@
         <v>44952</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65336,7 +65336,7 @@
         <v>45313</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>45341</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65487,7 +65487,7 @@
         <v>45622</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65560,7 +65560,7 @@
         <v>45316</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65633,7 +65633,7 @@
         <v>45610</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>44888</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>45560</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65862,7 +65862,7 @@
         <v>45313</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>45774</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>45774</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>45282</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66159,7 +66159,7 @@
         <v>45666</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>45272</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66310,7 +66310,7 @@
         <v>45735</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66383,7 +66383,7 @@
         <v>45099</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>44817</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66534,7 +66534,7 @@
         <v>45266</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66612,7 +66612,7 @@
         <v>45734</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>44988</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66768,7 +66768,7 @@
         <v>45599</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66841,7 +66841,7 @@
         <v>44607</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45020</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>44638</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67075,7 +67075,7 @@
         <v>45386</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67153,7 +67153,7 @@
         <v>45638</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         <v>45250</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67309,7 +67309,7 @@
         <v>45021</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67387,7 +67387,7 @@
         <v>44943</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67465,7 +67465,7 @@
         <v>45755</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         <v>45834</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67616,7 +67616,7 @@
         <v>45755</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67689,7 +67689,7 @@
         <v>46168</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67762,7 +67762,7 @@
         <v>46247</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45488</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>45826</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45805</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>46100</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>44606</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>46051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44501</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44987</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45915</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45826</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44861</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45016</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>46204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>44498</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>44694</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44915</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45893</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45601</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45093</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45443</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>46205</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46204</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>46265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44960</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44559</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45016</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>46038</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45601</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45436</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>46057</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45960</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45357</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>45613</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45176</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45061</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>45562</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>46188</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>45280</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>45463</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45671</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45505</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44823</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>46006</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45568</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45936</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45811</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45939</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45955</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45839</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45208</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45204</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44970</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>46281</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>46281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>46090</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>46295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44977</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46297</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45021</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>45735</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44727</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>44519</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44615</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44808</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44803</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>44851</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>44859</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44795</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>44526</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44474</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44477</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44476</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>44694</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44585</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44678</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44476</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44795</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44519</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44861</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44662</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44686</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44503</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44781</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44498</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44472</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44816</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44711</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>44704</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>44704</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45735</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>44915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45488</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45643</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45218</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45316</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45443</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>45106</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45114</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45698</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44985</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45561</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44761</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45036</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45035</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>46001</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45320</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45597</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45517</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45099</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45147</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45559</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45092</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45611</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>44516</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>44698</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44935</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45476</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45892</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45895</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45071</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45894</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45791</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45894</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45895</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45635</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45104</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45120</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44592</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45901</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45898</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45944</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>46035</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45903</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>45903</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45266</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45903</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45426</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>46036</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45589</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>46036</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45589</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45604</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44671</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>46038</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46042</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45750</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45590</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45915</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45590</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46045</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45912</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>46049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45587</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45646</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45916</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>46051</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45799</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>44687</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45800</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>46051</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>46051</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45800</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45805</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45919</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44595</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45805</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45918</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>44922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45923</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45479</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>46055</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45481</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>46057</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45148</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>46056</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>46056</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>46057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>46057</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45485</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45463</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45926</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45177</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45930</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45443</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45932</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45329</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45329</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44984</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45266</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45679</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45770</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45932</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>44592</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44592</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>45637</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45937</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45799</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>46070</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45938</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45939</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45939</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45938</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45938</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>46073</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>46072</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46078</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46078</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45944</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45944</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45944</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>46078</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45944</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45944</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46078</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>44943</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45944</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44739</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45793</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45944</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45944</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45677</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45947</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45505</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>46078</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>46078</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45947</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45369</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45951</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45953</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45103</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45813</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45952</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45955</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>46086</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45954</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45955</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46085</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45576</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45705</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45541</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45481</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45005</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45775</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>44866</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45265</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>45121</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>46094</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45068</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45463</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45967</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45205</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>45966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46093</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>46093</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45817</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45966</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45316</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45973</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45975</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45223</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>46104</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44908</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45975</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45814</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45814</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45975</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45463</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45979</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45505</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45981</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45113</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46107</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45985</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44952</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45985</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45985</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>46113</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45481</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45986</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46119</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45198</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44935</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>45993</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45826</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45553</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45215</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>44952</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45826</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45995</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45562</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>46128</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>46129</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45826</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>46129</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46129</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45996</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46112</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45826</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>46129</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>46001</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45826</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>46112</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>46128</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>46001</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>46132</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>46132</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>45831</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>46132</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>46132</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45105</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45833</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45832</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44936</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45832</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>45190</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45833</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45832</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45077</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45068</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45387</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45484</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45484</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45835</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45113</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45595</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45561</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>46136</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45463</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45839</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45839</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>44697</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44845</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45443</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>45488</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>45849</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45848</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45848</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45849</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45849</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45665</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45214</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>45981</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35738,7 +35738,7 @@
         <v>44971</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>46136</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45103</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45182</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45854</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45856</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45774</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45538</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>45856</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45481</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45356</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45523</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45698</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>45041</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>45329</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45867</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45867</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45484</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45484</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45565</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>45867</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44496</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45943</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45867</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>45867</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45868</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37726,7 +37726,7 @@
         <v>45868</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45868</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45112</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>45481</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>45154</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46142</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46142</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45198</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>46142</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>45329</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45756</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>46148</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>46148</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45870</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45665</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>46083</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45645</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45471</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45905</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45719</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45966</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>46155</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>45561</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45559</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46154</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>44524</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46090</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45635</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45502</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45645</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45546</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45566</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45566</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45756</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45121</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46160</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46160</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45743</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45604</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45029</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>46162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>46162</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46093</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>45825</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>46164</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44980</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45140</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45705</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41551,7 +41551,7 @@
         <v>46169</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45077</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>44505</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>44859</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>46174</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>46174</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>46171</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>46171</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>45883</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45883</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>45113</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>44551</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>46129</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45479</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>44938</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>46178</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45775</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45622</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45078</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45246</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>45189</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45379</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46185</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>46185</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>46188</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>46185</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>46185</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>46185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>46185</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46185</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45330</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>45448</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45774</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45560</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>46191</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>46191</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45149</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45551</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>46195</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45330</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45072</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45706</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46197</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45148</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46198</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>46201</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>46202</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>44952</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>46202</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>45135</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46202</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>46201</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>46202</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>46201</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>46202</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>46202</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>46202</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>46199</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>46202</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46202</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46199</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46204</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>46204</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45677</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45240</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>46205</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>46205</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>46204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>46204</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>46204</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46205</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46205</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45463</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45463</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46205</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46205</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45645</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46204</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>46209</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45476</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45160</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46208</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>46206</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>46208</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>46205</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>46206</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45443</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48358,7 +48358,7 @@
         <v>46205</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>46205</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>45506</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>46206</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>44826</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48743,7 +48743,7 @@
         <v>46209</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>44781</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45316</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>46209</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>46211</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45574</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>46211</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45103</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>44894</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>46212</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>46211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>46214</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49659,7 +49659,7 @@
         <v>45336</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>46258</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>46258</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>46258</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>46258</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>46258</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>46258</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>46258</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45194</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45684</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>46259</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>46259</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>46258</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45113</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>46258</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46259</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>46259</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>46258</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>46216</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46217</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>46261</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45463</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>46218</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45593</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46260</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46220</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>46262</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46262</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>45113</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46262</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45246</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46262</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45282</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>46267</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52359,7 +52359,7 @@
         <v>46267</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45524</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45524</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>46267</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>46267</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>46267</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46267</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>46267</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>46226</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>46269</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>46226</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45518</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53290,7 +53290,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>46268</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53446,7 +53446,7 @@
         <v>46268</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53524,7 +53524,7 @@
         <v>46226</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>46226</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>46268</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>46226</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>44992</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         <v>46269</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46268</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>46268</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45565</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54221,7 +54221,7 @@
         <v>46273</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>46272</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>46273</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>46273</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>46272</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>46232</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>46275</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>46275</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45154</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54986,7 +54986,7 @@
         <v>46281</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>46281</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>45448</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>46281</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45485</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>46281</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>46281</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55527,7 +55527,7 @@
         <v>46280</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>45093</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>46281</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>46281</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45545</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46281</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>46281</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>44993</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>46282</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>46282</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45712</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>46239</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>46240</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56536,7 +56536,7 @@
         <v>46240</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56614,7 +56614,7 @@
         <v>44879</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>44774</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56760,7 +56760,7 @@
         <v>46282</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>46282</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>45882</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>45619</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45387</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>46244</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>45428</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>46244</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>46286</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45756</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45645</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45748</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57681,7 +57681,7 @@
         <v>45492</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45705</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>45378</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>46289</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45357</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58066,7 +58066,7 @@
         <v>45566</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>46246</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>46265</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>46288</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>45545</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45576</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>46288</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45329</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58675,7 +58675,7 @@
         <v>46289</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>45526</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>46248</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58909,7 +58909,7 @@
         <v>45476</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>46290</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>46290</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>46290</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59211,7 +59211,7 @@
         <v>46248</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>45560</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>46248</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45882</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59518,7 +59518,7 @@
         <v>45894</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45392</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59669,7 +59669,7 @@
         <v>45329</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46290</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>46293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>44988</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>44988</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>46247</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>46248</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>46290</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>46290</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>46290</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45239</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>46293</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60585,7 +60585,7 @@
         <v>46248</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60663,7 +60663,7 @@
         <v>46248</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60741,7 +60741,7 @@
         <v>45099</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>46293</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60897,7 +60897,7 @@
         <v>46248</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61053,7 +61053,7 @@
         <v>46252</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>46295</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61209,7 +61209,7 @@
         <v>45104</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61282,7 +61282,7 @@
         <v>45104</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45774</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61428,7 +61428,7 @@
         <v>46295</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>46251</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>46295</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>46295</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45113</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>46295</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45329</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61964,7 +61964,7 @@
         <v>46251</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62042,7 +62042,7 @@
         <v>46281</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62120,7 +62120,7 @@
         <v>45174</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62198,7 +62198,7 @@
         <v>46294</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>45092</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45560</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46297</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45481</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>46297</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>46255</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>46253</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62817,7 +62817,7 @@
         <v>44936</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>46297</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62968,7 +62968,7 @@
         <v>44888</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>46254</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>45014</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>46297</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63270,7 +63270,7 @@
         <v>46244</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63348,7 +63348,7 @@
         <v>46254</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63426,7 +63426,7 @@
         <v>46297</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63504,7 +63504,7 @@
         <v>45590</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>46297</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>46255</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63733,7 +63733,7 @@
         <v>44925</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>46211</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>46253</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>46297</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>46254</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64118,7 +64118,7 @@
         <v>46255</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45189</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45282</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>44953</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64420,7 +64420,7 @@
         <v>44908</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45187</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45481</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         <v>45505</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         <v>45114</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64800,7 +64800,7 @@
         <v>45098</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64878,7 +64878,7 @@
         <v>45712</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64956,7 +64956,7 @@
         <v>45167</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>45576</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65107,7 +65107,7 @@
         <v>45534</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65185,7 +65185,7 @@
         <v>45484</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65263,7 +65263,7 @@
         <v>44952</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65336,7 +65336,7 @@
         <v>45313</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>45341</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65487,7 +65487,7 @@
         <v>45622</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65560,7 +65560,7 @@
         <v>45316</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65633,7 +65633,7 @@
         <v>45610</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>44888</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>45560</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65862,7 +65862,7 @@
         <v>45313</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>45774</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>45774</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>45282</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66159,7 +66159,7 @@
         <v>45666</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>45272</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66310,7 +66310,7 @@
         <v>45735</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66383,7 +66383,7 @@
         <v>45099</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>44817</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66534,7 +66534,7 @@
         <v>45266</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66612,7 +66612,7 @@
         <v>45734</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>44988</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66768,7 +66768,7 @@
         <v>45599</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66841,7 +66841,7 @@
         <v>44607</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45020</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>44638</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67075,7 +67075,7 @@
         <v>45386</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67153,7 +67153,7 @@
         <v>45638</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         <v>45250</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67309,7 +67309,7 @@
         <v>45021</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67387,7 +67387,7 @@
         <v>44943</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67465,7 +67465,7 @@
         <v>45755</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         <v>45834</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67616,7 +67616,7 @@
         <v>45755</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67689,7 +67689,7 @@
         <v>46168</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67762,7 +67762,7 @@
         <v>46247</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45488</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45826</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46301</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44606</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46051</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44987</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45915</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45016</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>45106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>45826</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44861</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>46204</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44498</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44694</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>44915</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45443</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44960</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45893</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>45093</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45601</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46204</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>46265</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>46301</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>46301</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>44559</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45463</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45505</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45357</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45436</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>45016</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>45960</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45280</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45562</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45061</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>46038</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45601</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>46057</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>46188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>46301</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44970</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>45811</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45208</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45955</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45839</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>46006</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45568</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>46196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>46281</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>46281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46290</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46295</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>46297</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46258</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46258</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45021</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44727</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44519</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44776</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44615</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44808</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44803</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>44851</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44847</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44859</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44797</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44795</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44526</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44503</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44678</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44781</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44795</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44519</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44694</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44498</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44861</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44872</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44531</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44585</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44686</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45378</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>44866</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44711</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44704</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44704</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>45205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44952</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45148</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45488</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45369</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45336</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45610</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>45505</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45774</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45471</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45481</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45619</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>45734</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45428</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45684</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45329</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45149</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44943</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45341</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45756</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45379</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45329</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45329</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45265</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45561</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45679</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45463</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45463</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45223</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45590</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45113</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45246</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45538</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45182</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45113</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45121</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45611</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45206</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44953</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44505</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45272</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>45068</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45756</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>45492</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45392</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45104</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45883</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45463</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44908</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45092</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45534</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45883</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45566</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45560</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45551</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45705</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45443</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45330</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45505</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>44739</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>44894</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45576</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45463</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45154</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45135</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45476</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45113</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44938</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45488</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45545</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45484</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45443</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45481</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45443</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45889</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45889</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45894</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45894</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45892</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45895</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45479</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45898</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45463</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45476</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45313</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45154</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44980</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45901</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>44935</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45481</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45560</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45560</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45903</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45545</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45316</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44888</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45518</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45911</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45562</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45912</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45566</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45599</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45756</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44988</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44985</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45916</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45198</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45593</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45174</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45915</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44984</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44888</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45481</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45712</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45918</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45113</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45919</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45622</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44952</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45443</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45923</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45484</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45698</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45775</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45120</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45114</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45923</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45560</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45330</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45926</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45791</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45329</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44524</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45476</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45194</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45565</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45930</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45706</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44551</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45426</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45320</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44936</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44592</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45665</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45750</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45595</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45587</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45190</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45099</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45506</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45932</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45932</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45485</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45622</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45316</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45800</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45448</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44595</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45448</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45937</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45597</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45938</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45705</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45517</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45218</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45805</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45805</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45938</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45937</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45645</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45805</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45643</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45799</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45645</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45937</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45177</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45106</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45937</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45463</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45939</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>44952</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45944</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45944</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45944</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45944</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45944</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45770</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45944</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45214</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45098</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45944</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45944</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45677</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45946</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45793</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45559</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45559</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45814</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45814</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45240</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45813</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44697</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45950</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45817</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45149</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45005</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45147</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>44698</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45947</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45099</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45947</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45481</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45826</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45826</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45826</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45826</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45774</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45774</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45826</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45952</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45561</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45826</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45826</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45479</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45103</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45103</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44971</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45239</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45160</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45951</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45832</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45832</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45666</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45832</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45831</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45953</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45953</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45832</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45954</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>45955</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45955</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45833</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45833</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45014</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45187</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>44774</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45838</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45112</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>44761</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44687</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45966</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45966</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45839</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45637</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45565</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45966</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>44671</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45839</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45968</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45114</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45967</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45968</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>44845</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45113</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>44826</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45665</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45971</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45265</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45848</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45848</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45743</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45973</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45849</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45849</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45719</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45313</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45849</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45854</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45975</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45856</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45029</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>45266</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45266</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45856</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45103</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45975</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45357</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45174</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45484</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45975</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45867</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45868</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45867</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45867</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45775</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45868</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45868</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45867</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45978</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45282</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45870</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45980</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>44781</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>44922</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45748</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45484</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45979</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45463</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45463</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45774</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45093</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45981</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45698</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45985</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45985</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>44988</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>44988</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45246</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45985</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45985</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45282</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45215</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45677</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44879</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45485</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45645</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45986</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>46104</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45985</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>46107</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45316</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>45316</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>45574</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45523</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45481</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45735</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45526</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45077</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45481</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>45524</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45524</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45329</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>46113</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45068</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>46119</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45546</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45993</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>44925</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>44952</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45995</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45387</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45387</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45735</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45996</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>46001</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>46112</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46001</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>46112</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>46128</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>46129</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>44935</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>46132</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>46129</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>46132</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46001</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>46129</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>46129</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>46132</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45576</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45561</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>46132</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45266</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>46128</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>44993</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>46006</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45072</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45078</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46136</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>46136</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45774</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45105</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45908</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45944</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45943</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46036</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>46035</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46036</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45589</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45589</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45604</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>46038</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>46042</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45167</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45867</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45981</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45590</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45590</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45635</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45113</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45356</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44516</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>46048</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45505</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>46045</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45646</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>46142</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>46049</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>44496</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45329</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45329</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>46051</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>46051</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>46051</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46056</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>46055</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>46056</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
         <v>46057</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>46057</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46057</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>46142</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46142</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46148</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>46148</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46070</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44592</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>44592</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>46072</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>46073</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>46073</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>46076</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45905</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45966</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>46154</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>46078</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>46078</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>46078</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>46078</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46078</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46078</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>46078</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>46083</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>46085</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>46084</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>46155</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>46160</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>46086</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45502</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>46160</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45635</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>46093</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>46093</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45604</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45645</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51231,7 +51231,7 @@
         <v>46162</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>46094</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>46094</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>46090</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46162</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46164</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>46093</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51757,7 +51757,7 @@
         <v>45825</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>46168</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>46171</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>46171</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>46174</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>46174</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>46129</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>46178</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>46185</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>46185</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52600,7 +52600,7 @@
         <v>46185</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>46185</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>46185</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>46185</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>46185</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46188</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>46191</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53146,7 +53146,7 @@
         <v>46195</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>46201</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>46199</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>46201</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46201</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>46199</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46198</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46202</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46202</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46202</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>46202</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>46202</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>46202</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>46202</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>46202</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>46202</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54379,7 +54379,7 @@
         <v>46204</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>46204</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>46204</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46204</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>46205</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>46205</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>46205</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>46205</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>46204</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>46205</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>46205</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>46205</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>46205</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>46204</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55441,7 +55441,7 @@
         <v>46205</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55519,7 +55519,7 @@
         <v>46209</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>46206</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>46206</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>46206</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>46206</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>46208</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>46208</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56055,7 +56055,7 @@
         <v>46209</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56128,7 +56128,7 @@
         <v>46209</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56201,7 +56201,7 @@
         <v>46211</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56279,7 +56279,7 @@
         <v>46211</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>46211</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>46212</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>46214</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56591,7 +56591,7 @@
         <v>46218</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56664,7 +56664,7 @@
         <v>46217</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56737,7 +56737,7 @@
         <v>46216</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>46220</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>46268</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>46268</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>46268</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>46268</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57205,7 +57205,7 @@
         <v>46267</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>46267</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>46267</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>46268</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>46267</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>46268</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>46267</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>46267</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>46267</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57907,7 +57907,7 @@
         <v>46269</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>46226</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>46226</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>46226</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58219,7 +58219,7 @@
         <v>46272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>46226</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>46226</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58448,7 +58448,7 @@
         <v>46269</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58526,7 +58526,7 @@
         <v>46272</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>46272</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>46273</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58755,7 +58755,7 @@
         <v>46273</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58833,7 +58833,7 @@
         <v>46273</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58911,7 +58911,7 @@
         <v>46275</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>46232</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59062,7 +59062,7 @@
         <v>46275</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>46280</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>46281</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>46282</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>46239</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46282</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>46281</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>46281</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>46281</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>46282</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46281</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>46281</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>46281</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>46281</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60149,7 +60149,7 @@
         <v>46281</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>46282</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60305,7 +60305,7 @@
         <v>46286</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>46240</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60461,7 +60461,7 @@
         <v>46240</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>45882</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>46244</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>46288</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60763,7 +60763,7 @@
         <v>46265</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>46244</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60914,7 +60914,7 @@
         <v>46288</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60987,7 +60987,7 @@
         <v>46290</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61060,7 +61060,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>45882</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61206,7 +61206,7 @@
         <v>46290</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61284,7 +61284,7 @@
         <v>46290</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61362,7 +61362,7 @@
         <v>46289</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>46290</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>46290</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61591,7 +61591,7 @@
         <v>46246</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>46289</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>46247</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>46248</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61898,7 +61898,7 @@
         <v>45894</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61971,7 +61971,7 @@
         <v>46290</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>46290</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62127,7 +62127,7 @@
         <v>46293</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>46248</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>46248</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46248</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>46248</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62517,7 +62517,7 @@
         <v>46248</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62595,7 +62595,7 @@
         <v>46248</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>46294</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46293</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>46293</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62907,7 +62907,7 @@
         <v>46295</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62985,7 +62985,7 @@
         <v>46253</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>46295</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63141,7 +63141,7 @@
         <v>46251</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63214,7 +63214,7 @@
         <v>46281</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>46251</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63370,7 +63370,7 @@
         <v>46252</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>46295</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63526,7 +63526,7 @@
         <v>46295</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63604,7 +63604,7 @@
         <v>46253</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63682,7 +63682,7 @@
         <v>46295</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63760,7 +63760,7 @@
         <v>46300</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63838,7 +63838,7 @@
         <v>45835</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63916,7 +63916,7 @@
         <v>46297</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>46297</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64072,7 +64072,7 @@
         <v>46211</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64145,7 +64145,7 @@
         <v>46300</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64223,7 +64223,7 @@
         <v>46300</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>46297</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64379,7 +64379,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>46244</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64535,7 +64535,7 @@
         <v>46191</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>46300</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>46254</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64769,7 +64769,7 @@
         <v>46300</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64847,7 +64847,7 @@
         <v>46297</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64925,7 +64925,7 @@
         <v>46297</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65003,7 +65003,7 @@
         <v>45911</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65081,7 +65081,7 @@
         <v>46255</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65154,7 +65154,7 @@
         <v>46297</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65232,7 +65232,7 @@
         <v>46300</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>46255</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65388,7 +65388,7 @@
         <v>46297</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>46300</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>46300</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65622,7 +65622,7 @@
         <v>46254</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>46300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65778,7 +65778,7 @@
         <v>46300</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         <v>46255</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65929,7 +65929,7 @@
         <v>46259</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46258</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66085,7 +66085,7 @@
         <v>46258</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66163,7 +66163,7 @@
         <v>46258</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66241,7 +66241,7 @@
         <v>46301</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66319,7 +66319,7 @@
         <v>46301</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>46302</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66475,7 +66475,7 @@
         <v>46259</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66553,7 +66553,7 @@
         <v>46258</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>46301</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66709,7 +66709,7 @@
         <v>46258</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66787,7 +66787,7 @@
         <v>46258</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66865,7 +66865,7 @@
         <v>46301</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66938,7 +66938,7 @@
         <v>46301</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67016,7 +67016,7 @@
         <v>46301</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67094,7 +67094,7 @@
         <v>46259</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67172,7 +67172,7 @@
         <v>46258</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>46258</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>46259</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67406,7 +67406,7 @@
         <v>46301</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67484,7 +67484,7 @@
         <v>46258</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67562,7 +67562,7 @@
         <v>46258</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>46262</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67718,7 +67718,7 @@
         <v>46261</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67796,7 +67796,7 @@
         <v>46303</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67874,7 +67874,7 @@
         <v>46262</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67952,7 +67952,7 @@
         <v>46262</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68030,7 +68030,7 @@
         <v>46262</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68108,7 +68108,7 @@
         <v>46260</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68186,7 +68186,7 @@
         <v>44607</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>44638</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68342,7 +68342,7 @@
         <v>45020</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68420,7 +68420,7 @@
         <v>45386</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68498,7 +68498,7 @@
         <v>45638</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68576,7 +68576,7 @@
         <v>45250</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68654,7 +68654,7 @@
         <v>45021</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68732,7 +68732,7 @@
         <v>44943</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68810,7 +68810,7 @@
         <v>45755</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68883,7 +68883,7 @@
         <v>45834</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68961,7 +68961,7 @@
         <v>45755</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69034,7 +69034,7 @@
         <v>46168</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69107,7 +69107,7 @@
         <v>46247</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45488</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45826</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46301</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44606</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46051</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>44501</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44987</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45915</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45016</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>45106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>45826</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>44861</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>46204</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46301</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44498</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44694</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>44915</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45443</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44960</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45893</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>45093</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45601</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46204</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>46265</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>46301</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>46301</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>44559</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45463</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45505</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45357</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45436</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>45016</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>45960</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45280</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45562</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45061</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>46038</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45601</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>46057</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>46188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>46301</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>44970</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>45811</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45208</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45955</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45839</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45236</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>46006</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45568</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>46196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>46281</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>46281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>46090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46290</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46295</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>46297</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46258</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46258</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45021</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44727</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44519</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44776</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44615</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44808</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44803</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>44851</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44847</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44859</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44797</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44795</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44526</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44503</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44678</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44781</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44795</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44519</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44694</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44498</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44861</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44872</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44531</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44585</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44686</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45378</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>44866</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44711</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44704</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44704</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>45205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44952</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45148</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45488</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45369</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45336</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45610</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>45505</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45774</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45471</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45481</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45619</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>45734</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45428</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45684</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45329</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45149</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44943</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45341</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45756</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45379</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45329</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45329</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45265</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45561</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45679</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45463</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45463</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45223</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45590</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45113</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45246</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45538</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45182</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45113</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45121</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45611</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45206</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44953</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44505</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45272</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>45068</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45756</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>45492</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45392</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45104</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45883</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45463</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44908</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45092</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45534</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45883</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45566</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45560</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45551</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45705</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45443</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45330</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45505</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>44739</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>44894</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45576</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45463</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45154</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45135</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45476</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45113</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44938</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45488</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45545</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45484</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45443</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45481</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45443</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45889</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45889</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45894</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45894</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45892</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45895</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45479</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45898</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45463</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45476</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45313</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45154</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44980</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45901</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>44935</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45481</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45560</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45560</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45903</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45545</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45316</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45121</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>44971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>44888</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45518</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45911</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45562</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45912</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45566</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45599</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45756</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44988</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44985</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45916</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45198</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45593</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45174</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45915</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44984</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44888</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45481</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45712</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45918</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45113</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45919</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45922</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45622</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44952</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45443</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45923</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45484</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45698</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45775</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45120</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45114</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45923</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45560</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45330</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45926</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45791</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45329</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44524</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45476</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45194</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45565</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45930</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45706</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44551</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45426</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45320</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>44936</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44592</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45665</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45750</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45595</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45587</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45190</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45099</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45506</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45932</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45932</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45485</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45622</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45316</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45800</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45448</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44595</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45448</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45937</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45597</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45938</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45705</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45517</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45218</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45805</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45938</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45805</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45938</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45937</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45645</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45805</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45643</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45799</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45645</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45937</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45177</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45106</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45937</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45463</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45939</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45939</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>44952</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45944</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45944</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45944</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45944</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45944</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45770</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45944</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45214</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45098</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45944</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45944</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45677</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45946</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45793</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45559</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45559</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45814</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45814</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45240</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45813</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44697</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45950</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45817</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45149</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45005</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45147</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>44698</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45947</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45099</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45947</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45481</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45826</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45826</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45826</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45826</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45774</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45774</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45826</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45952</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45561</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45826</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45826</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45479</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45103</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45103</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44971</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45239</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45160</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45951</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45832</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45832</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45666</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45832</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45831</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45953</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45953</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45832</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45954</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>45955</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45955</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45833</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45833</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34836,7 +34836,7 @@
         <v>45014</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45187</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>45174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>44774</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45838</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45112</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>44761</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44687</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45966</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45966</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45839</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45637</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45565</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45966</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>44671</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45839</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45968</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45114</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45967</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45968</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>44845</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45113</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>44826</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45665</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45971</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45265</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45848</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45848</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45743</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45973</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45849</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45849</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45719</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45313</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45849</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45854</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45975</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45856</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45029</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>45266</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45266</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45856</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45103</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45975</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45357</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45174</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45484</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45975</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45867</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45868</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45867</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45867</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45775</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45868</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45868</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45867</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45978</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45282</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45870</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45980</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>44781</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>44922</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45748</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45484</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45979</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45463</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45463</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45774</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>45093</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45981</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45698</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45985</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45985</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>44988</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>44988</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45246</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45985</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45985</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45282</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45215</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45677</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>44879</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45485</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45645</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45986</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>46104</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45985</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>46107</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45316</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>45316</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>45574</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45523</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45481</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>45735</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45526</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45077</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45481</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>45524</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45524</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45329</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>46113</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45068</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>46119</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45546</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45993</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>44925</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>44952</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45995</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43309,7 +43309,7 @@
         <v>45387</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45387</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45735</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45996</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>46001</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>46112</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46001</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>46112</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>46128</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>46129</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>44935</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>46132</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>46129</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>46132</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46001</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>46129</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>46129</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>46132</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45576</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45561</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>46132</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45266</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>46128</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>44993</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>46006</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45072</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45078</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46136</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>46136</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45774</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45105</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45908</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45944</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45943</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46036</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>46035</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46036</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45589</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45589</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45604</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>46038</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>46042</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45167</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45867</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45981</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45590</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45590</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45635</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45113</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45356</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44516</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>46048</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45505</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>46045</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45646</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>46142</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>46049</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>44496</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45329</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45329</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>46051</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>46051</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>46051</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46056</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>46055</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>46056</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
         <v>46057</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>46057</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46057</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>46142</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46142</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46148</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>46148</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46070</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44592</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>44592</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>46072</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>46073</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>46073</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>46076</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45905</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45966</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>46154</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>46078</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>46078</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>46078</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>46078</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46078</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46078</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>46078</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>46083</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>46085</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>46084</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>46155</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>46160</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>46086</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45502</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>46160</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45635</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>46093</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>46093</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45604</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45645</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51231,7 +51231,7 @@
         <v>46162</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>46094</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>46094</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>46090</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46162</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46164</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>46093</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51757,7 +51757,7 @@
         <v>45825</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>46168</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>46171</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>46171</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>46174</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>46174</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>46129</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>46178</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>46185</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>46185</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52600,7 +52600,7 @@
         <v>46185</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>46185</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>46185</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52834,7 +52834,7 @@
         <v>46185</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>46185</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46188</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>46191</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53146,7 +53146,7 @@
         <v>46195</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>46201</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>46199</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>46201</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46201</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>46199</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46198</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46202</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>46202</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46202</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>46202</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>46202</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>46202</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>46202</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>46202</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>46202</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54379,7 +54379,7 @@
         <v>46204</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>46204</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>46204</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46204</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>46205</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>46205</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>46205</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>46205</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>46204</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>46205</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>46205</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>46205</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>46205</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>46204</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55441,7 +55441,7 @@
         <v>46205</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55519,7 +55519,7 @@
         <v>46209</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55592,7 +55592,7 @@
         <v>46206</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>46206</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>46206</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>46206</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>46208</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>46208</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56055,7 +56055,7 @@
         <v>46209</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56128,7 +56128,7 @@
         <v>46209</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56201,7 +56201,7 @@
         <v>46211</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56279,7 +56279,7 @@
         <v>46211</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>46211</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>46212</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>46214</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56591,7 +56591,7 @@
         <v>46218</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56664,7 +56664,7 @@
         <v>46217</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56737,7 +56737,7 @@
         <v>46216</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>46220</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>46268</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>46268</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>46268</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>46268</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57205,7 +57205,7 @@
         <v>46267</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>46267</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>46267</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>46268</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>46267</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>46268</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>46267</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>46267</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>46267</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57907,7 +57907,7 @@
         <v>46269</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>46226</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>46226</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>46226</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58219,7 +58219,7 @@
         <v>46272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>46226</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>46226</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58448,7 +58448,7 @@
         <v>46269</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58526,7 +58526,7 @@
         <v>46272</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>46272</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>46273</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58755,7 +58755,7 @@
         <v>46273</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58833,7 +58833,7 @@
         <v>46273</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58911,7 +58911,7 @@
         <v>46275</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>46232</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59062,7 +59062,7 @@
         <v>46275</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>46280</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>46281</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>46282</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>46239</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46282</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>46281</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>46281</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>46281</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>46282</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46281</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>46281</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>46281</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>46281</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60149,7 +60149,7 @@
         <v>46281</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>46282</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60305,7 +60305,7 @@
         <v>46286</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>46240</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60461,7 +60461,7 @@
         <v>46240</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>45882</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>46244</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>46288</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60763,7 +60763,7 @@
         <v>46265</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>46244</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60914,7 +60914,7 @@
         <v>46288</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60987,7 +60987,7 @@
         <v>46290</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61060,7 +61060,7 @@
         <v>46290</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>45882</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61206,7 +61206,7 @@
         <v>46290</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61284,7 +61284,7 @@
         <v>46290</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61362,7 +61362,7 @@
         <v>46289</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>46290</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>46290</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61591,7 +61591,7 @@
         <v>46246</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>46289</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>46247</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>46248</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61898,7 +61898,7 @@
         <v>45894</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61971,7 +61971,7 @@
         <v>46290</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>46290</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62127,7 +62127,7 @@
         <v>46293</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62205,7 +62205,7 @@
         <v>46248</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62283,7 +62283,7 @@
         <v>46248</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46248</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>46248</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62517,7 +62517,7 @@
         <v>46248</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62595,7 +62595,7 @@
         <v>46248</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>46294</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46293</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>46293</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62907,7 +62907,7 @@
         <v>46295</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62985,7 +62985,7 @@
         <v>46253</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>46295</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63141,7 +63141,7 @@
         <v>46251</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63214,7 +63214,7 @@
         <v>46281</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>46251</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63370,7 +63370,7 @@
         <v>46252</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63448,7 +63448,7 @@
         <v>46295</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63526,7 +63526,7 @@
         <v>46295</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63604,7 +63604,7 @@
         <v>46253</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63682,7 +63682,7 @@
         <v>46295</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63760,7 +63760,7 @@
         <v>46300</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63838,7 +63838,7 @@
         <v>45835</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63916,7 +63916,7 @@
         <v>46297</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>46297</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64072,7 +64072,7 @@
         <v>46211</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64145,7 +64145,7 @@
         <v>46300</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64223,7 +64223,7 @@
         <v>46300</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>46297</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64379,7 +64379,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64457,7 +64457,7 @@
         <v>46244</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64535,7 +64535,7 @@
         <v>46191</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>46300</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>46254</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64769,7 +64769,7 @@
         <v>46300</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64847,7 +64847,7 @@
         <v>46297</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64925,7 +64925,7 @@
         <v>46297</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65003,7 +65003,7 @@
         <v>45911</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65081,7 +65081,7 @@
         <v>46255</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65154,7 +65154,7 @@
         <v>46297</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65232,7 +65232,7 @@
         <v>46300</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>46255</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65388,7 +65388,7 @@
         <v>46297</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>46300</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>46300</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65622,7 +65622,7 @@
         <v>46254</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>46300</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65778,7 +65778,7 @@
         <v>46300</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         <v>46255</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65929,7 +65929,7 @@
         <v>46259</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46258</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66085,7 +66085,7 @@
         <v>46258</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66163,7 +66163,7 @@
         <v>46258</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66241,7 +66241,7 @@
         <v>46301</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66319,7 +66319,7 @@
         <v>46301</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>46302</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66475,7 +66475,7 @@
         <v>46259</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66553,7 +66553,7 @@
         <v>46258</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>46301</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66709,7 +66709,7 @@
         <v>46258</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66787,7 +66787,7 @@
         <v>46258</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66865,7 +66865,7 @@
         <v>46301</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66938,7 +66938,7 @@
         <v>46301</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67016,7 +67016,7 @@
         <v>46301</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67094,7 +67094,7 @@
         <v>46259</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67172,7 +67172,7 @@
         <v>46258</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>46258</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>46259</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67406,7 +67406,7 @@
         <v>46301</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67484,7 +67484,7 @@
         <v>46258</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67562,7 +67562,7 @@
         <v>46258</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>46262</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67718,7 +67718,7 @@
         <v>46261</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67796,7 +67796,7 @@
         <v>46303</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67874,7 +67874,7 @@
         <v>46262</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67952,7 +67952,7 @@
         <v>46262</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68030,7 +68030,7 @@
         <v>46262</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68108,7 +68108,7 @@
         <v>46260</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68186,7 +68186,7 @@
         <v>44607</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>44638</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68342,7 +68342,7 @@
         <v>45020</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68420,7 +68420,7 @@
         <v>45386</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68498,7 +68498,7 @@
         <v>45638</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68576,7 +68576,7 @@
         <v>45250</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68654,7 +68654,7 @@
         <v>45021</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68732,7 +68732,7 @@
         <v>44943</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68810,7 +68810,7 @@
         <v>45755</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68883,7 +68883,7 @@
         <v>45834</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68961,7 +68961,7 @@
         <v>45755</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69034,7 +69034,7 @@
         <v>46168</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69107,7 +69107,7 @@
         <v>46247</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>46301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45826</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>46100</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44606</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44501</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44987</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45915</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44861</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45016</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>46204</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45826</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44498</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45093</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45893</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>45601</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45443</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44960</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>46204</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46301</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>44559</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46309</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45016</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45357</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>45613</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>45176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45061</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45562</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>46038</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>45601</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>46057</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45280</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45463</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45671</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45505</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>46301</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45208</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45936</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45955</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44970</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>46006</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45568</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44817</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45236</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>46281</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44977</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>46281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46090</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>46295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>46297</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>46309</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45811</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45826</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45839</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45021</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44519</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44615</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44776</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44808</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44803</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44851</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>44847</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44859</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44797</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44795</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>44817</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44694</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44585</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44678</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>44755</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44795</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44519</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44861</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44872</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44531</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44686</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44781</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44498</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44711</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44704</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44704</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45735</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>44915</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>45488</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45643</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45106</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45316</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45443</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45114</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45218</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45698</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45561</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44761</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45035</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45320</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45597</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45517</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45099</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45147</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44516</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45092</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45611</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44935</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45071</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45635</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45104</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45120</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44592</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45266</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45426</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44671</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>44687</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44922</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45479</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45481</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45177</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45485</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45463</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45463</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>44971</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44984</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45266</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>45637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45679</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45770</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>44943</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44739</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45677</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45103</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45505</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45369</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45443</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45576</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45005</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45705</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45481</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45775</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44866</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45121</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45265</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45068</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45463</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45205</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45316</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44908</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45223</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45206</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45463</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45505</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45113</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>44952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45329</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45329</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45481</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44935</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>46136</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45553</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45215</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44952</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45889</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45889</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45476</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45562</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45892</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45895</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45894</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45894</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45894</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45895</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44936</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45190</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45149</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45077</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45901</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45068</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44496</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45387</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45943</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45898</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45903</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45903</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45903</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45484</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45484</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45595</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45561</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45463</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45909</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45908</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45911</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>45911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>46142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44697</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>46142</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45912</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46142</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45916</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45919</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45443</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45918</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45922</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45488</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45923</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45665</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46148</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45214</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>46148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45926</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>44971</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45103</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45930</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45932</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>46083</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45932</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45182</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45799</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45938</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45937</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45774</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45939</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45538</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45938</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45938</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45481</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45944</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45944</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45356</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45944</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45944</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45944</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45944</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45793</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45944</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45523</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45698</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45946</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45905</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45947</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45329</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45947</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>45966</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45950</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>45951</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45952</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>46154</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45955</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45954</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45955</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45484</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45484</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45565</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>46090</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45635</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45502</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45645</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45112</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45967</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45481</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>45966</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45966</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>45154</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45966</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>46160</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45971</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45968</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>46160</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45968</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45973</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45329</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45975</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45975</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45604</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45756</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45665</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>46162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45978</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45979</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>46162</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45645</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>46093</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45471</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45719</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45561</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45985</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45559</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45825</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>46164</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44524</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45546</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>46169</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>46168</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45993</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45566</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45566</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45756</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45121</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45743</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45995</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45996</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>46001</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>46001</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>44980</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>46001</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45140</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45705</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45077</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>44505</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46006</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>44859</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>46174</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>46174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>46171</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>46171</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44551</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45479</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>44938</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45775</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45622</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45078</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45246</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45189</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45379</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45944</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>46035</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46036</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45589</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>46036</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45589</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45604</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>46178</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46038</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>45330</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45448</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>46042</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45774</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45590</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>46045</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45560</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46049</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45646</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>46048</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46051</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45149</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46051</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46051</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46055</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45551</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>46057</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46056</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45330</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45072</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46056</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>46057</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46057</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45706</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45148</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44952</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>44592</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45135</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46185</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>46185</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>44592</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46188</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>46070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>46185</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>46185</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46185</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>46185</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46185</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>46073</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45677</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>46073</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46072</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45240</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>46078</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>46078</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46078</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46078</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46078</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45463</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45463</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>46076</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45645</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46078</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46078</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45476</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>46084</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45160</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45443</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46086</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46085</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45506</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>44826</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44781</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45316</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>45574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45103</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>44894</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46094</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>46191</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>46093</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46093</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45336</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45194</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45684</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45113</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46104</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45174</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45463</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45593</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>46195</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46107</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45113</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46198</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45246</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46113</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>45282</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>46119</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>46201</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>46202</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>46202</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45524</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45524</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>46202</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45518</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>46201</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>46202</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>46201</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>46202</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>46128</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>44992</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>46202</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>46202</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>46129</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>45565</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>46129</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>46129</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>46112</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46129</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>46112</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>46199</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>46202</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>46202</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>46199</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>46132</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>46132</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>46204</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>46204</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>46132</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>46132</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>46205</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>46205</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>46204</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>46204</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>46204</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>46205</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>46205</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>46205</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>46205</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>45154</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>46204</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>45448</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>46136</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45485</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46209</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45093</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>46206</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45545</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>44993</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>46208</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>46206</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45712</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>46208</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46205</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46206</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>46205</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46205</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>46206</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46209</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>44879</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44774</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46209</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>46211</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45619</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45387</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>46211</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46212</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>46211</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>46214</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45428</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>46216</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>46217</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>46218</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45756</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45645</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>46220</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45748</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>45492</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45705</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45378</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45357</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45566</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46226</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46226</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>46226</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>46226</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45545</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45576</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>46273</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45329</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45526</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>46272</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>46272</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45476</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46273</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>46273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45560</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>46272</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45392</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>45329</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>44988</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44988</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45239</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>46232</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46275</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46275</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45099</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45104</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45104</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45774</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45113</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>46281</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         <v>46281</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>46281</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45329</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>45174</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>46281</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45092</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>46281</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>46280</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51292,7 +51292,7 @@
         <v>45560</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45481</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46281</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>46281</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>46281</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>46281</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>46282</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46282</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>44936</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>44888</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>46239</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>46240</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45014</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52286,7 +52286,7 @@
         <v>46240</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>46282</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46282</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45590</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>44925</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45882</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45189</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45282</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>44953</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>46244</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>44908</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45187</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>45481</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>45505</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>45114</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>46244</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45098</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>46286</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53665,7 +53665,7 @@
         <v>46289</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45712</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45167</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46246</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45576</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>46288</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>45534</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>46288</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54274,7 +54274,7 @@
         <v>46289</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>46248</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>46290</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>45484</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>46248</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>46248</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45882</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45894</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>44952</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>46290</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>46293</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>46247</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>46248</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>46290</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>46290</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55565,7 +55565,7 @@
         <v>46290</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>46293</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45313</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45341</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>46248</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45622</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>46248</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>46248</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>46290</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45316</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>46252</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>46295</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56564,7 +56564,7 @@
         <v>46295</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>46251</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>45610</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>46295</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>46295</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56949,7 +56949,7 @@
         <v>46295</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>46251</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57105,7 +57105,7 @@
         <v>44888</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57178,7 +57178,7 @@
         <v>46294</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45560</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45313</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>45774</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>45774</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57558,7 +57558,7 @@
         <v>45282</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57631,7 +57631,7 @@
         <v>46297</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57709,7 +57709,7 @@
         <v>46297</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45666</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57860,7 +57860,7 @@
         <v>45272</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57938,7 +57938,7 @@
         <v>45735</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         <v>46253</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>46297</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>45099</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46254</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58318,7 +58318,7 @@
         <v>46297</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46244</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>44817</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>46254</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>46297</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58708,7 +58708,7 @@
         <v>46297</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>46211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>46253</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>46297</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>46254</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45835</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>45266</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>46258</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>46258</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59405,7 +59405,7 @@
         <v>46301</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>46300</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59561,7 +59561,7 @@
         <v>46300</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45734</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59717,7 +59717,7 @@
         <v>46301</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>46258</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46301</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>46301</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>46255</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46255</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>44988</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60336,7 +60336,7 @@
         <v>46258</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60414,7 +60414,7 @@
         <v>46258</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45599</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>46300</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>46300</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>46258</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>46301</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46300</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60950,7 +60950,7 @@
         <v>45911</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61028,7 +61028,7 @@
         <v>46258</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61106,7 +61106,7 @@
         <v>46301</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>46300</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>46258</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>46258</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>46258</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>46301</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>46300</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61652,7 +61652,7 @@
         <v>46191</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61730,7 +61730,7 @@
         <v>46300</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>46300</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>46255</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>46259</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62037,7 +62037,7 @@
         <v>46303</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>46302</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62193,7 +62193,7 @@
         <v>46259</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62271,7 +62271,7 @@
         <v>46259</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62349,7 +62349,7 @@
         <v>46260</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45791</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>46259</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>46307</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>46262</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>45750</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>46094</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>46262</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62963,7 +62963,7 @@
         <v>46262</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>45799</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>46261</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45800</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63275,7 +63275,7 @@
         <v>46262</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63353,7 +63353,7 @@
         <v>46307</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63426,7 +63426,7 @@
         <v>46309</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63504,7 +63504,7 @@
         <v>46307</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>46281</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>46265</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>45805</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>46308</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63879,7 +63879,7 @@
         <v>46309</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63957,7 +63957,7 @@
         <v>44595</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45805</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64108,7 +64108,7 @@
         <v>45805</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64186,7 +64186,7 @@
         <v>46309</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>46309</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>46309</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64420,7 +64420,7 @@
         <v>46267</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>46267</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64576,7 +64576,7 @@
         <v>45813</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>46268</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>46269</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>45541</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>46268</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>46267</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65044,7 +65044,7 @@
         <v>46267</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>45817</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45814</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45814</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>46267</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65424,7 +65424,7 @@
         <v>46268</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>46268</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65580,7 +65580,7 @@
         <v>46311</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65658,7 +65658,7 @@
         <v>46269</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65736,7 +65736,7 @@
         <v>45826</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65814,7 +65814,7 @@
         <v>46267</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65892,7 +65892,7 @@
         <v>46268</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65970,7 +65970,7 @@
         <v>46268</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66048,7 +66048,7 @@
         <v>45826</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>45826</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45826</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66282,7 +66282,7 @@
         <v>46267</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66360,7 +66360,7 @@
         <v>45826</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66438,7 +66438,7 @@
         <v>45826</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>45826</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66594,7 +66594,7 @@
         <v>45831</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66667,7 +66667,7 @@
         <v>45833</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>45832</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66818,7 +66818,7 @@
         <v>45832</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45833</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66969,7 +66969,7 @@
         <v>45832</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67042,7 +67042,7 @@
         <v>45832</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67115,7 +67115,7 @@
         <v>45838</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67193,7 +67193,7 @@
         <v>45839</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>45839</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67349,7 +67349,7 @@
         <v>44845</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67427,7 +67427,7 @@
         <v>45849</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67505,7 +67505,7 @@
         <v>45848</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67578,7 +67578,7 @@
         <v>45848</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67651,7 +67651,7 @@
         <v>45849</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67729,7 +67729,7 @@
         <v>45849</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67802,7 +67802,7 @@
         <v>45854</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45856</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67958,7 +67958,7 @@
         <v>45856</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45867</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68114,7 +68114,7 @@
         <v>45867</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68192,7 +68192,7 @@
         <v>45867</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68270,7 +68270,7 @@
         <v>45867</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68348,7 +68348,7 @@
         <v>45868</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68426,7 +68426,7 @@
         <v>45868</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68504,7 +68504,7 @@
         <v>45868</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68582,7 +68582,7 @@
         <v>45870</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>45883</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         <v>45883</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68816,7 +68816,7 @@
         <v>44607</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68894,7 +68894,7 @@
         <v>45020</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>44638</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69050,7 +69050,7 @@
         <v>45386</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>45638</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69206,7 +69206,7 @@
         <v>45250</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>45021</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69362,7 +69362,7 @@
         <v>44943</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69440,7 +69440,7 @@
         <v>45755</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69513,7 +69513,7 @@
         <v>45834</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69591,7 +69591,7 @@
         <v>45755</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>46168</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69737,7 +69737,7 @@
         <v>46247</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46309</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>46301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45826</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>46100</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44606</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44501</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44987</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45915</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44861</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45016</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45106</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>46204</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45826</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44498</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44915</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45093</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45893</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>45601</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45443</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>44960</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>46204</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46301</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>44559</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46309</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45016</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45357</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>45613</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>45176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45061</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45562</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>46038</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>45601</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>46057</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45280</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>46188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45463</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45671</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45505</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>46301</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45208</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45936</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>45939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>45955</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44970</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>46006</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45568</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>44817</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45236</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>46281</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44977</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>46281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46090</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46290</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>46295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>46297</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>46309</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45811</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45826</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45839</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45021</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>44727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44519</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44615</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44776</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44808</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44803</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44851</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>44847</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44859</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44797</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44795</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>44817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>44817</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44694</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44585</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44678</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>44755</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44795</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44519</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44861</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44872</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44531</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44686</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>44781</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44498</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44711</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44816</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44704</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44704</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45735</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>44915</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>45488</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45643</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45106</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45316</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45443</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45114</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45218</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45698</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45561</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44761</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45035</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45320</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45597</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45517</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45099</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45147</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44516</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45092</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45611</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44935</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45071</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45635</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45104</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45120</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44592</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45266</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45426</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>44671</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>44687</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44922</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45479</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45481</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45177</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45485</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45463</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45463</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>44971</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>44984</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45266</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>45637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45679</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45770</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>44943</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44739</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45677</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45103</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45505</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45369</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45443</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45576</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45005</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45705</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45481</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45775</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44866</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45121</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45265</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45068</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45463</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45205</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45316</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44908</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45223</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45206</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45463</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45505</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45113</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>44952</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45329</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45329</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45481</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44935</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>46136</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45553</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45215</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44952</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45889</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45889</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45476</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45562</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45892</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45895</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45894</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45894</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45894</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45895</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44936</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45190</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45149</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45077</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45901</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45068</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44496</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45387</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45943</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45898</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45903</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21847,7 +21847,7 @@
         <v>45903</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45903</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45484</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45484</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45595</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45561</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45463</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45909</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45908</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45911</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>45911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>46142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44697</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>46142</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45912</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46142</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45916</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45919</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45443</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45918</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45922</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45488</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45923</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45665</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46148</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45214</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>46148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45926</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>44971</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45103</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45930</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45932</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>46083</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45932</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45182</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45799</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45938</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45937</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45774</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45939</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45538</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45938</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45938</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45481</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45944</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45944</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45356</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45944</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45944</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45944</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45944</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45793</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45944</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45523</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45698</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45946</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45905</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45947</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45329</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45947</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>45966</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45950</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>45951</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45952</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>46154</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45955</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45954</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45955</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45484</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45484</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45565</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>46090</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45635</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45502</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45645</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45112</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45967</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45481</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>45966</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45966</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>45154</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45966</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>46160</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45971</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45968</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>46160</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45968</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45973</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45329</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45975</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45975</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45975</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45604</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45756</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45665</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>46162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45978</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45979</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>46162</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45645</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>46093</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45471</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45719</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45561</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45985</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45559</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45825</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>46164</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44524</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45546</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>46169</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>46168</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45993</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45566</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45566</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45756</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45121</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45743</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45995</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45996</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>46001</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>46001</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>44980</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>46001</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45140</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45705</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45077</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>44505</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46006</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>44859</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>46174</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>46174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>46171</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>46171</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44551</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45479</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>44938</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45775</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45622</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45078</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45246</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45189</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45379</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45944</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>46035</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46036</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45589</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>46036</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45589</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45604</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>46178</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46038</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>45330</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35350,7 +35350,7 @@
         <v>45448</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>46042</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45774</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45590</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>46045</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45560</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46049</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45646</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>46048</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46051</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45149</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46051</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46051</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46055</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45551</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>46057</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46056</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45330</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>45072</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46056</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>46057</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46057</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45706</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45148</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44952</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>44592</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45135</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46185</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>46185</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>44592</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46188</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>46070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>46185</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>46185</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46185</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>46185</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46185</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>46073</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45677</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>46073</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46072</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45240</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>46078</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>46078</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46078</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46078</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46078</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45463</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45463</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>46076</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45645</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46078</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46078</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45476</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>46084</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45160</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45443</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46086</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46085</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45506</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>44826</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44781</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45316</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>45574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45103</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>44894</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46094</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>46191</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>46093</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46093</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45336</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45194</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45684</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45113</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46104</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>45174</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45463</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45593</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>46195</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46107</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45113</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46198</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45246</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46113</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>45282</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>46119</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>46201</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>46202</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>46202</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45524</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45524</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>46202</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45518</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>46201</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>46202</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>46201</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>46202</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>46128</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>44992</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>46202</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>46202</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>46129</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>45565</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>46129</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>46129</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>46112</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>46129</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>46112</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>46199</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>46202</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>46202</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>46199</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>46132</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>46132</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>46204</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>46204</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>46132</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>46132</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>46205</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>46205</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>46204</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>46204</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>46204</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>46205</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>46205</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>46205</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>46205</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>45154</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>46204</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45240,7 +45240,7 @@
         <v>45448</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>46136</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>45485</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46209</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45093</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>46206</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45545</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>44993</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>46208</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>46206</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45712</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>46208</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46205</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46206</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>46205</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46205</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>46206</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46209</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>44879</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44774</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46209</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>46211</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45619</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45387</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>46211</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46212</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>46211</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>46214</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45428</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>46216</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>46217</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>46218</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45756</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45645</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>46220</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45748</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>45492</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45705</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45378</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45357</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45566</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46226</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46226</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>46226</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>46226</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45545</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45576</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>46273</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45329</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45526</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>46272</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>46272</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45476</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46273</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>46273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45560</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>46272</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45392</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>45329</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>44988</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44988</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45239</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>46232</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46275</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46275</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45099</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45104</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45104</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45774</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45113</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>46281</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         <v>46281</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>46281</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45329</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>45174</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>46281</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45092</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>46281</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>46280</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51292,7 +51292,7 @@
         <v>45560</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45481</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46281</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>46281</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>46281</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>46281</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>46282</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46282</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>44936</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>44888</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>46239</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>46240</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45014</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52286,7 +52286,7 @@
         <v>46240</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>46282</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46282</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45590</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>44925</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45882</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45189</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45282</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>44953</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>46244</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>44908</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45187</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>45481</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>45505</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>45114</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>46244</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45098</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>46286</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53665,7 +53665,7 @@
         <v>46289</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45712</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45167</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>46246</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45576</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>46288</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>45534</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>46288</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54274,7 +54274,7 @@
         <v>46289</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>46248</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>46290</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>45484</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>46248</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>46248</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45882</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45894</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>44952</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>46290</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55180,7 +55180,7 @@
         <v>46293</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>46247</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>46248</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>46290</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>46290</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55565,7 +55565,7 @@
         <v>46290</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>46293</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45313</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45341</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>46248</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45622</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>46248</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>46248</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>46290</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45316</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>46252</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>46295</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56564,7 +56564,7 @@
         <v>46295</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>46251</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>45610</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>46295</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>46295</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56949,7 +56949,7 @@
         <v>46295</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>46251</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57105,7 +57105,7 @@
         <v>44888</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57178,7 +57178,7 @@
         <v>46294</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45560</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>45313</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57412,7 +57412,7 @@
         <v>45774</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>45774</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57558,7 +57558,7 @@
         <v>45282</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57631,7 +57631,7 @@
         <v>46297</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57709,7 +57709,7 @@
         <v>46297</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45666</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57860,7 +57860,7 @@
         <v>45272</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57938,7 +57938,7 @@
         <v>45735</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         <v>46253</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>46297</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>45099</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46254</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58318,7 +58318,7 @@
         <v>46297</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46244</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>44817</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>46254</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>46297</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58708,7 +58708,7 @@
         <v>46297</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>46211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>46253</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>46297</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>46254</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>45835</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>45266</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>46258</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59327,7 +59327,7 @@
         <v>46258</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59405,7 +59405,7 @@
         <v>46301</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>46300</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59561,7 +59561,7 @@
         <v>46300</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45734</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59717,7 +59717,7 @@
         <v>46301</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>46258</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46301</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>46301</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>46255</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46255</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>44988</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60336,7 +60336,7 @@
         <v>46258</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60414,7 +60414,7 @@
         <v>46258</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45599</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>46300</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>46300</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>46258</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>46301</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46300</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60950,7 +60950,7 @@
         <v>45911</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61028,7 +61028,7 @@
         <v>46258</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61106,7 +61106,7 @@
         <v>46301</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>46300</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>46258</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>46258</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>46258</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>46301</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>46300</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61652,7 +61652,7 @@
         <v>46191</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61730,7 +61730,7 @@
         <v>46300</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>46300</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>46255</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>46259</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62037,7 +62037,7 @@
         <v>46303</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>46302</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62193,7 +62193,7 @@
         <v>46259</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62271,7 +62271,7 @@
         <v>46259</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62349,7 +62349,7 @@
         <v>46260</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45791</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>46259</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>46307</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>46262</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>45750</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>46094</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>46262</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62963,7 +62963,7 @@
         <v>46262</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>45799</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>46261</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45800</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63275,7 +63275,7 @@
         <v>46262</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63353,7 +63353,7 @@
         <v>46307</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63426,7 +63426,7 @@
         <v>46309</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63504,7 +63504,7 @@
         <v>46307</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63577,7 +63577,7 @@
         <v>46281</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>46265</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>45805</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>46308</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63879,7 +63879,7 @@
         <v>46309</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63957,7 +63957,7 @@
         <v>44595</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45805</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64108,7 +64108,7 @@
         <v>45805</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64186,7 +64186,7 @@
         <v>46309</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>46309</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>46309</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64420,7 +64420,7 @@
         <v>46267</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>46267</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64576,7 +64576,7 @@
         <v>45813</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>46268</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>46269</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>45541</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>46268</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>46267</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65044,7 +65044,7 @@
         <v>46267</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>45817</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45814</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45814</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>46267</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65424,7 +65424,7 @@
         <v>46268</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>46268</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65580,7 +65580,7 @@
         <v>46311</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65658,7 +65658,7 @@
         <v>46269</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65736,7 +65736,7 @@
         <v>45826</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65814,7 +65814,7 @@
         <v>46267</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65892,7 +65892,7 @@
         <v>46268</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65970,7 +65970,7 @@
         <v>46268</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66048,7 +66048,7 @@
         <v>45826</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>45826</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45826</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66282,7 +66282,7 @@
         <v>46267</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66360,7 +66360,7 @@
         <v>45826</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66438,7 +66438,7 @@
         <v>45826</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>45826</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66594,7 +66594,7 @@
         <v>45831</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66667,7 +66667,7 @@
         <v>45833</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66745,7 +66745,7 @@
         <v>45832</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66818,7 +66818,7 @@
         <v>45832</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>45833</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66969,7 +66969,7 @@
         <v>45832</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67042,7 +67042,7 @@
         <v>45832</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67115,7 +67115,7 @@
         <v>45838</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67193,7 +67193,7 @@
         <v>45839</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>45839</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67349,7 +67349,7 @@
         <v>44845</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67427,7 +67427,7 @@
         <v>45849</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67505,7 +67505,7 @@
         <v>45848</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67578,7 +67578,7 @@
         <v>45848</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67651,7 +67651,7 @@
         <v>45849</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67729,7 +67729,7 @@
         <v>45849</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67802,7 +67802,7 @@
         <v>45854</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67880,7 +67880,7 @@
         <v>45856</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67958,7 +67958,7 @@
         <v>45856</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45867</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68114,7 +68114,7 @@
         <v>45867</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68192,7 +68192,7 @@
         <v>45867</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68270,7 +68270,7 @@
         <v>45867</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68348,7 +68348,7 @@
         <v>45868</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68426,7 +68426,7 @@
         <v>45868</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68504,7 +68504,7 @@
         <v>45868</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68582,7 +68582,7 @@
         <v>45870</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>45883</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         <v>45883</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68816,7 +68816,7 @@
         <v>44607</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68894,7 +68894,7 @@
         <v>45020</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>44638</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69050,7 +69050,7 @@
         <v>45386</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69128,7 +69128,7 @@
         <v>45638</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69206,7 +69206,7 @@
         <v>45250</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         <v>45021</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69362,7 +69362,7 @@
         <v>44943</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69440,7 +69440,7 @@
         <v>45755</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69513,7 +69513,7 @@
         <v>45834</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69591,7 +69591,7 @@
         <v>45755</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>46168</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69737,7 +69737,7 @@
         <v>46247</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69815,7 +69815,7 @@
         <v>46309</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45826</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>46301</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>46100</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44606</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44501</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>46204</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45826</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>46301</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>44861</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44987</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45016</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44498</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45893</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45443</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>44960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44915</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>46204</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45601</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46301</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46265</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45093</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>44559</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46309</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45061</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45960</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46188</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45357</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45463</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45436</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>46038</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45601</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>46057</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45505</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>45176</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>46301</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45016</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>45280</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45562</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45936</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45939</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45955</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46006</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>46281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45568</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>46090</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>46290</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45805</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45811</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>46295</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45839</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>46297</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>46258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>46258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>46258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>46309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>46281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46317</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>46318</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45236</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44977</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45204</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45208</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>45021</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45735</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44727</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>44615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44776</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44808</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44803</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44851</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44847</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44859</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44795</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>44817</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44817</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44694</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44585</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44678</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44755</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44795</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44519</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44861</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44662</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44531</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44686</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44872</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44781</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44498</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>44711</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44816</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44704</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44704</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>45476</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45619</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45329</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45329</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45072</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45894</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45894</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45892</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45894</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45078</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45895</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>45895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45883</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45206</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>45068</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45901</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45378</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>44866</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45901</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45205</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45774</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45903</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>46160</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45635</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45604</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45645</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>46162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45911</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45912</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46090</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45911</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45915</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>46162</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45918</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46164</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45919</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45923</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45167</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>46093</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45825</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45113</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45356</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44516</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>46169</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45930</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45369</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45336</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>46171</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>46171</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>46174</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45932</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45932</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45505</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45937</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45938</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45938</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45937</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45799</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45329</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45329</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45937</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45937</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45939</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45939</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45939</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45944</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45944</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45734</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45428</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45944</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45944</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45944</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45148</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45944</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45488</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45463</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45463</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45610</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45946</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45223</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45505</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>44859</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45113</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45774</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45471</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45793</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45481</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>44953</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46178</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45947</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45947</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45684</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45952</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45077</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45953</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>45329</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45954</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45955</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>46185</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>46185</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46185</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45265</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45955</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46185</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46185</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46185</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45590</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45246</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45092</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45392</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45071</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45611</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>46188</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45966</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45492</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45968</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45967</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45968</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46191</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46195</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45971</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45148</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45534</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45566</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>46201</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45560</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45705</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>46199</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45975</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45975</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>46201</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>46201</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45975</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46199</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>46198</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45330</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45978</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45505</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45980</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>46202</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>45979</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44739</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>46202</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45576</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45463</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>46202</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>46202</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>44938</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45576</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45463</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>46204</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46204</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>46204</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>46204</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46205</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46205</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45985</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44908</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46205</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>46204</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>46205</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>46205</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>46205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>45985</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>46204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>46205</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45985</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45986</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45985</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>46209</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>46206</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45463</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>46208</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>45313</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>46208</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46209</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45154</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>46209</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>46211</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>46211</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45092</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>46212</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>46214</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45551</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45993</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45995</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46218</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45996</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46217</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46216</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46001</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>46220</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>46001</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>46001</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45443</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45599</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>44988</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46226</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46226</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>46226</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46226</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>46232</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>46280</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>46282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>46282</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>46281</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46281</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>46281</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46282</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45526</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>46281</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46281</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>46281</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>46282</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45791</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46286</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>46240</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45944</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46240</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46036</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>46035</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>46036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45589</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45589</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45604</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>46038</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46042</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45750</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45882</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45590</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45590</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>46244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>46288</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46244</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45154</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46048</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46288</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46045</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45646</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>46049</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>46290</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>46290</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45800</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45882</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46290</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45799</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44595</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46051</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>46051</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46051</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>45135</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46290</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46289</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46290</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>46056</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>46246</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45805</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>46055</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46056</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>46057</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46247</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>46057</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>46057</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>46248</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45894</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>46290</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>46290</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>46293</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45541</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>46248</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46248</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>46248</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46248</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>46248</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45814</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45814</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45813</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>46248</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>45817</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>46294</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>46070</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>44592</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44592</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>46293</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46293</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46072</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>46073</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>46073</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>46295</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46076</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>46253</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>46295</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>45826</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45826</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46251</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>46078</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>46078</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>45826</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>45826</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>46078</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45826</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46078</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45484</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45826</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45826</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46078</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>46078</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46251</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>46252</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46078</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46295</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>46295</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>45832</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>46253</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45443</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>46295</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>46085</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45832</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45832</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>46300</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45835</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>46084</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45831</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42025,7 +42025,7 @@
         <v>45832</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>46297</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>46297</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45833</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46211</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45833</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>46300</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>46300</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46086</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46297</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46254</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>46244</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>46191</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45838</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>46300</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>46254</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>46300</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46297</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>46297</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>45911</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45839</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>46093</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>46093</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>46297</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>46300</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46255</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46094</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45839</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>44936</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>45174</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45481</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>45443</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46297</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>46300</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>44845</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>46300</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46254</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>46300</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>46300</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>46255</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45479</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>46259</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45848</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45848</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>46104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45476</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46258</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46258</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>46258</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>46301</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>46301</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>46107</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>46302</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45849</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45849</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>46259</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>46258</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>46301</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45849</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>46258</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45854</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>46258</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>46301</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45856</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45856</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>46301</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>46301</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>44980</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46259</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>46258</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>46258</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>46259</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>46301</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>44935</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47805,7 +47805,7 @@
         <v>46258</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>46258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>46113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45481</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>46119</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45867</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48273,7 +48273,7 @@
         <v>45868</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45867</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45867</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>46261</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45868</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>45868</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>45867</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>46303</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45870</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>46112</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>46112</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>46260</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>46128</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>46129</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>46132</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>46262</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>46129</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>46132</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>46308</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>46129</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
         <v>46129</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>46132</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>46132</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>45545</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>45316</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>46262</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>46262</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>46307</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>45883</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46265</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>44888</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>45518</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>46094</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45566</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>46262</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>44915</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>44985</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>44992</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>46307</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>45198</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>44984</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>44888</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>44908</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>46281</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>46136</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>45481</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>46307</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46136</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>46267</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>46309</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46309</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52156,7 +52156,7 @@
         <v>46267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>46309</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>46267</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>46267</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>46309</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>46309</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>46267</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>46267</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>46268</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>46268</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45908</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>44952</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46312</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>46314</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53233,7 +53233,7 @@
         <v>46268</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>46268</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45114</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45943</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>46269</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53613,7 +53613,7 @@
         <v>46311</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>46268</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53847,7 +53847,7 @@
         <v>46269</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>46312</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>46267</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>46314</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44524</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45867</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>46273</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54383,7 +54383,7 @@
         <v>45194</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54456,7 +54456,7 @@
         <v>45565</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54534,7 +54534,7 @@
         <v>45981</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>46272</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>45706</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>46272</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>46273</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>45553</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55060,7 +55060,7 @@
         <v>45320</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55133,7 +55133,7 @@
         <v>44936</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55206,7 +55206,7 @@
         <v>44592</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>46273</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>46317</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45595</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45587</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>46142</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>44496</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>46318</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>46142</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>46142</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>46309</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46318</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56132,7 +56132,7 @@
         <v>45448</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>46275</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>46275</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>46318</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>46148</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56522,7 +56522,7 @@
         <v>45448</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>46148</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45705</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>45705</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>45218</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>45905</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45966</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>46154</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45463</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>44952</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46083</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45559</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45559</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57506,7 +57506,7 @@
         <v>46155</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>44697</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>46160</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45005</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45502</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57891,7 +57891,7 @@
         <v>45099</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57969,7 +57969,7 @@
         <v>44817</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45481</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45479</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>44971</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>45666</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>45014</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58422,7 +58422,7 @@
         <v>45112</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58500,7 +58500,7 @@
         <v>45565</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
         <v>45114</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45113</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45665</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45029</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>45140</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>45103</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45174</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45775</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45748</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45484</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>45774</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45093</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>45698</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>44988</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>44988</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>45566</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45523</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>45481</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59942,7 +59942,7 @@
         <v>45735</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45077</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60093,7 +60093,7 @@
         <v>45524</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45524</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45068</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45149</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>44943</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45341</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45756</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60624,7 +60624,7 @@
         <v>45379</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60702,7 +60702,7 @@
         <v>45561</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45679</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60853,7 +60853,7 @@
         <v>45104</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45538</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45182</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45113</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45121</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61238,7 +61238,7 @@
         <v>44505</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>45272</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>45756</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45104</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>45104</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>45099</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>44894</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>45488</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>45545</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45560</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62003,7 +62003,7 @@
         <v>45560</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45121</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62159,7 +62159,7 @@
         <v>44971</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45562</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45756</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>45593</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>45174</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62539,7 +62539,7 @@
         <v>45712</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>45041</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62690,7 +62690,7 @@
         <v>45113</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62768,7 +62768,7 @@
         <v>45622</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45443</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>45484</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62997,7 +62997,7 @@
         <v>45484</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>45698</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>45775</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         <v>45120</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45560</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45330</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63450,7 +63450,7 @@
         <v>45329</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45712</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45476</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45036</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>45035</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>44551</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45426</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>45665</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64059,7 +64059,7 @@
         <v>45190</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45099</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45506</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>45485</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>45622</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45316</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>45597</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64580,7 +64580,7 @@
         <v>45517</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64653,7 +64653,7 @@
         <v>45645</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45643</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64804,7 +64804,7 @@
         <v>45645</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64877,7 +64877,7 @@
         <v>45177</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64955,7 +64955,7 @@
         <v>45106</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>45770</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>45214</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>45098</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>45677</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45240</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65418,7 +65418,7 @@
         <v>45149</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65496,7 +65496,7 @@
         <v>45147</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65569,7 +65569,7 @@
         <v>44698</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65647,7 +65647,7 @@
         <v>45774</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65720,7 +65720,7 @@
         <v>45774</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45561</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65866,7 +65866,7 @@
         <v>45103</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65944,7 +65944,7 @@
         <v>45103</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66022,7 +66022,7 @@
         <v>45189</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66095,7 +66095,7 @@
         <v>45239</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>45160</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66246,7 +66246,7 @@
         <v>45187</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66319,7 +66319,7 @@
         <v>45174</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>44774</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66470,7 +66470,7 @@
         <v>44761</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66548,7 +66548,7 @@
         <v>44687</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66626,7 +66626,7 @@
         <v>45637</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66699,7 +66699,7 @@
         <v>45198</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66777,7 +66777,7 @@
         <v>44671</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66850,7 +66850,7 @@
         <v>44826</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66928,7 +66928,7 @@
         <v>45265</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67006,7 +67006,7 @@
         <v>45743</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67084,7 +67084,7 @@
         <v>45719</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67157,7 +67157,7 @@
         <v>45313</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67235,7 +67235,7 @@
         <v>45266</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67313,7 +67313,7 @@
         <v>45266</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67391,7 +67391,7 @@
         <v>45357</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>45484</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67547,7 +67547,7 @@
         <v>45282</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67620,7 +67620,7 @@
         <v>44781</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67693,7 +67693,7 @@
         <v>44922</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67771,7 +67771,7 @@
         <v>45463</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67849,7 +67849,7 @@
         <v>45463</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67927,7 +67927,7 @@
         <v>45246</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>45282</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>45215</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68161,7 +68161,7 @@
         <v>45677</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68234,7 +68234,7 @@
         <v>44879</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68307,7 +68307,7 @@
         <v>45485</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68380,7 +68380,7 @@
         <v>45645</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>45316</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>45316</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68599,7 +68599,7 @@
         <v>45574</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68677,7 +68677,7 @@
         <v>45526</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68755,7 +68755,7 @@
         <v>45481</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45329</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68911,7 +68911,7 @@
         <v>45546</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68989,7 +68989,7 @@
         <v>44925</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69067,7 +69067,7 @@
         <v>44952</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>45387</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69218,7 +69218,7 @@
         <v>45387</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69296,7 +69296,7 @@
         <v>45735</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69369,7 +69369,7 @@
         <v>44935</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69447,7 +69447,7 @@
         <v>45576</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69525,7 +69525,7 @@
         <v>45561</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69598,7 +69598,7 @@
         <v>45266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69676,7 +69676,7 @@
         <v>44993</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69754,7 +69754,7 @@
         <v>44607</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69832,7 +69832,7 @@
         <v>44638</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69910,7 +69910,7 @@
         <v>45020</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69988,7 +69988,7 @@
         <v>45386</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70066,7 +70066,7 @@
         <v>45638</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70144,7 +70144,7 @@
         <v>45250</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70222,7 +70222,7 @@
         <v>45021</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70300,7 +70300,7 @@
         <v>44943</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70378,7 +70378,7 @@
         <v>45755</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70451,7 +70451,7 @@
         <v>45834</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70529,7 +70529,7 @@
         <v>45755</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70602,7 +70602,7 @@
         <v>46168</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>46247</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70753,7 +70753,7 @@
         <v>46309</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70831,7 +70831,7 @@
         <v>46316</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -601,7 +601,7 @@
         <v>45481</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45481</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45201</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>45965</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>44986</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>44713</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44960</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45826</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>46301</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>46100</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>45805</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>44606</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46051</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44501</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>46204</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45826</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>46301</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>44861</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44987</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45016</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44498</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44694</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45893</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45443</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>44960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44915</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>46204</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45601</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46301</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46301</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46265</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45093</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>44559</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46309</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45061</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>45960</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46188</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45357</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45463</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45436</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>46038</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45601</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>46057</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45505</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>45176</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>46301</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45016</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>45280</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45562</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44823</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>45936</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45939</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45955</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44970</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46006</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>46281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45568</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>46090</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>46290</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45805</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45811</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>46295</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45839</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>46297</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>46258</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>46258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>46258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>46309</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>46281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>46317</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>46318</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45236</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44977</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45204</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45208</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>45021</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45735</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44727</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>44615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44776</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44808</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44803</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44851</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44847</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44859</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44795</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44526</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>44817</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44817</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44694</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44585</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44678</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44755</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44795</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44519</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44861</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44662</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44531</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44686</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>44872</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44781</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44498</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>44711</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44816</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44704</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44704</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>45476</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45619</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45329</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45329</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45072</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45894</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45894</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45892</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45894</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45078</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45895</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>45895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45883</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45206</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>45068</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45901</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45378</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>44866</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45901</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45205</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45774</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45903</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>46160</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45635</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45604</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45645</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>46162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45911</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45912</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46090</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45911</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45915</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>46162</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45918</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46164</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45919</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45923</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45167</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>46093</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45825</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45113</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45356</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44516</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>46169</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45930</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45369</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45336</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>46171</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>46171</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>46174</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45932</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45932</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45505</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45937</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>45938</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45938</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45937</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45799</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45329</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45329</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45937</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45937</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45939</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45939</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45939</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45944</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45944</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45944</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45734</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45428</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45944</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45944</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45944</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45148</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45944</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45488</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45463</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45463</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45610</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45946</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45223</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45505</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>44859</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45113</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45774</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45471</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45793</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45481</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>44953</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46178</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45947</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45947</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45684</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>45952</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45077</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45953</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>45329</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45954</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>45955</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>46185</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>46185</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46185</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45265</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45955</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46185</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46185</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46185</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45590</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>45246</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45092</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45392</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45071</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45611</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>46188</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45966</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45492</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45968</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45967</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45968</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46191</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46195</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45971</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45148</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45534</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>45566</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>46201</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45560</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45705</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>46199</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45975</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45975</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>46201</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>46201</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45975</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46199</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>46198</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45330</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45978</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45505</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45980</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>46202</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>45979</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44739</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>46202</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45576</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45463</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>46202</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>46202</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46202</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>44938</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45576</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45463</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>46204</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>46204</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>46204</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>46204</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46205</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46205</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45985</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44908</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46205</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>46204</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>46205</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>46205</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>46205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>45985</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>46204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>46205</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45985</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45986</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>45985</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>46209</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>46206</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>46206</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45463</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>46208</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>45313</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>46208</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>46209</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45154</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>46209</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>46211</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>46211</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45092</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>46212</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>46214</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>45551</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45993</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45995</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46218</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45996</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46217</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>46216</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46001</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>46220</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>46001</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>46001</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45443</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45599</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>44988</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46226</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46226</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>46226</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46226</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>46232</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>46280</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>46282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46239</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>46282</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>46281</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46281</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>46281</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46282</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45526</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>46281</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46281</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>46281</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>46281</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>46282</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45791</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46286</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>46240</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45944</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46240</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46036</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>46035</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>46036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45589</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45589</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45604</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>46038</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46042</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45750</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45882</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45590</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45590</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>46244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>46288</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46244</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45154</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46048</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46288</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46045</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45646</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>46049</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>46290</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>46290</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45800</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45882</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46290</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45799</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44595</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46051</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>46051</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46051</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>45135</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46290</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46289</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46290</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45805</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>46056</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>46246</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45805</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>46055</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46056</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>46057</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46247</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>46057</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>46057</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>46248</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45894</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>46290</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>46290</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>46293</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45541</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>46248</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46248</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>46248</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46248</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>46248</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45814</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45814</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45813</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>46248</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>45817</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>46294</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>46070</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>44592</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44592</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>46293</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46293</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46072</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>46073</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>46073</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>46295</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46076</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>46253</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>46295</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>45826</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45826</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46251</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>46078</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>46078</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>45826</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>45826</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>46078</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45826</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46078</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45484</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45826</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45826</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46078</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>46078</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46251</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>46252</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46078</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46295</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>46295</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>45832</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>46253</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45443</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>46295</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>46085</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45832</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45832</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>46300</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45835</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>46084</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45831</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42025,7 +42025,7 @@
         <v>45832</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>46297</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>46297</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45833</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46211</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45833</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>46300</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>46300</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46086</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46297</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46254</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>46244</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>46191</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45838</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>46300</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>46254</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>46300</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46297</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>46297</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>45911</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45839</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>46093</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>46093</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>46297</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>46300</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46255</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46094</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45839</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>44936</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>45174</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45481</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>45443</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46297</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>46300</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>44845</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>46300</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46254</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>46300</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>46300</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>46255</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45479</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>46259</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45848</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45848</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>46104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45476</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46258</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46258</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>46258</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>46301</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>46301</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>46107</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>46302</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45849</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>45849</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>46259</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>46258</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>46301</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45849</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>46258</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45854</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>46258</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>46301</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45856</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45856</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>46301</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>46301</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>44980</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46259</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>46258</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>46258</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>46259</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>46301</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>44935</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47805,7 +47805,7 @@
         <v>46258</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>46258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>46113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45481</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>46119</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45867</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48273,7 +48273,7 @@
         <v>45868</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45867</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45867</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>46261</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45868</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>45868</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>45867</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>46303</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45870</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>46112</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>46112</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>46260</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>46128</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>46129</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>46132</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>46262</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>46129</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>46132</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>46308</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>46129</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
         <v>46129</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>46132</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>46132</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>45545</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>45316</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>46262</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>46262</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>46307</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>45883</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46265</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>44888</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>45518</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>46094</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45566</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>46262</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>44915</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>44985</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>44992</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>46307</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>45198</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>44984</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>44888</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>44908</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>46281</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>46136</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>45481</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>46307</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46136</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>46267</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>46309</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46309</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52156,7 +52156,7 @@
         <v>46267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52234,7 +52234,7 @@
         <v>46309</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>46267</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>46267</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>46309</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>46309</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>46267</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>46267</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52780,7 +52780,7 @@
         <v>46268</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>46268</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45908</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>44952</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46312</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>46314</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53233,7 +53233,7 @@
         <v>46268</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>46268</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45114</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45943</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>46269</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53613,7 +53613,7 @@
         <v>46311</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>46268</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53847,7 +53847,7 @@
         <v>46269</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>46312</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>46267</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>46314</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44524</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45867</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>46273</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54383,7 +54383,7 @@
         <v>45194</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54456,7 +54456,7 @@
         <v>45565</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54534,7 +54534,7 @@
         <v>45981</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>46272</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>45706</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>46272</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>46273</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>45553</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55060,7 +55060,7 @@
         <v>45320</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55133,7 +55133,7 @@
         <v>44936</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55206,7 +55206,7 @@
         <v>44592</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55279,7 +55279,7 @@
         <v>46273</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>46317</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45595</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55513,7 +55513,7 @@
         <v>45587</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>46142</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>44496</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>46318</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>46142</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>46142</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>46309</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46318</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56132,7 +56132,7 @@
         <v>45448</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>46275</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>46275</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>46318</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>46148</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56522,7 +56522,7 @@
         <v>45448</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>46148</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45705</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>45705</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>45218</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>45905</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45966</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>46154</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45463</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>44952</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46083</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45559</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45559</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57506,7 +57506,7 @@
         <v>46155</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>44697</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>46160</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45005</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45502</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57891,7 +57891,7 @@
         <v>45099</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57969,7 +57969,7 @@
         <v>44817</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45481</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45479</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>44971</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>45666</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>45014</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58422,7 +58422,7 @@
         <v>45112</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58500,7 +58500,7 @@
         <v>45565</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
         <v>45114</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45113</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45665</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45029</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>45140</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>45103</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45174</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45775</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45748</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45484</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>45774</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45093</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>45698</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>44988</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>44988</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>45566</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45523</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>45481</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59942,7 +59942,7 @@
         <v>45735</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45077</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60093,7 +60093,7 @@
         <v>45524</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45524</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45068</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45149</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>44943</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45341</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45756</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60624,7 +60624,7 @@
         <v>45379</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60702,7 +60702,7 @@
         <v>45561</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45679</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60853,7 +60853,7 @@
         <v>45104</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45538</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45182</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45113</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45121</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61238,7 +61238,7 @@
         <v>44505</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>45272</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>45756</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45104</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>45104</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61618,7 +61618,7 @@
         <v>45099</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>44894</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>45488</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>45545</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45560</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62003,7 +62003,7 @@
         <v>45560</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45121</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62159,7 +62159,7 @@
         <v>44971</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45562</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45756</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>45593</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>45174</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62539,7 +62539,7 @@
         <v>45712</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>45041</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62690,7 +62690,7 @@
         <v>45113</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62768,7 +62768,7 @@
         <v>45622</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45443</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>45484</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62997,7 +62997,7 @@
         <v>45484</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>45698</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>45775</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         <v>45120</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45560</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45330</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63450,7 +63450,7 @@
         <v>45329</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45712</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45476</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45036</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>45035</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>44551</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45426</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>45665</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64059,7 +64059,7 @@
         <v>45190</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45099</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45506</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>45485</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>45622</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45316</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>45597</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64580,7 +64580,7 @@
         <v>45517</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64653,7 +64653,7 @@
         <v>45645</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45643</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64804,7 +64804,7 @@
         <v>45645</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64877,7 +64877,7 @@
         <v>45177</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64955,7 +64955,7 @@
         <v>45106</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>45770</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>45214</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>45098</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>45677</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45240</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65418,7 +65418,7 @@
         <v>45149</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65496,7 +65496,7 @@
         <v>45147</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65569,7 +65569,7 @@
         <v>44698</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65647,7 +65647,7 @@
         <v>45774</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65720,7 +65720,7 @@
         <v>45774</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45561</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65866,7 +65866,7 @@
         <v>45103</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65944,7 +65944,7 @@
         <v>45103</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66022,7 +66022,7 @@
         <v>45189</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66095,7 +66095,7 @@
         <v>45239</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>45160</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66246,7 +66246,7 @@
         <v>45187</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66319,7 +66319,7 @@
         <v>45174</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>44774</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66470,7 +66470,7 @@
         <v>44761</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66548,7 +66548,7 @@
         <v>44687</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66626,7 +66626,7 @@
         <v>45637</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66699,7 +66699,7 @@
         <v>45198</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66777,7 +66777,7 @@
         <v>44671</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66850,7 +66850,7 @@
         <v>44826</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66928,7 +66928,7 @@
         <v>45265</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67006,7 +67006,7 @@
         <v>45743</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67084,7 +67084,7 @@
         <v>45719</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67157,7 +67157,7 @@
         <v>45313</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67235,7 +67235,7 @@
         <v>45266</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67313,7 +67313,7 @@
         <v>45266</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67391,7 +67391,7 @@
         <v>45357</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67469,7 +67469,7 @@
         <v>45484</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67547,7 +67547,7 @@
         <v>45282</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -67620,7 +67620,7 @@
         <v>44781</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -67693,7 +67693,7 @@
         <v>44922</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -67771,7 +67771,7 @@
         <v>45463</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67849,7 +67849,7 @@
         <v>45463</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67927,7 +67927,7 @@
         <v>45246</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>45282</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>45215</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -68161,7 +68161,7 @@
         <v>45677</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -68234,7 +68234,7 @@
         <v>44879</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -68307,7 +68307,7 @@
         <v>45485</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -68380,7 +68380,7 @@
         <v>45645</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>45316</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>45316</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -68599,7 +68599,7 @@
         <v>45574</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -68677,7 +68677,7 @@
         <v>45526</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -68755,7 +68755,7 @@
         <v>45481</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45329</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68911,7 +68911,7 @@
         <v>45546</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68989,7 +68989,7 @@
         <v>44925</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69067,7 +69067,7 @@
         <v>44952</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>45387</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -69218,7 +69218,7 @@
         <v>45387</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -69296,7 +69296,7 @@
         <v>45735</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -69369,7 +69369,7 @@
         <v>44935</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -69447,7 +69447,7 @@
         <v>45576</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -69525,7 +69525,7 @@
         <v>45561</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -69598,7 +69598,7 @@
         <v>45266</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -69676,7 +69676,7 @@
         <v>44993</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -69754,7 +69754,7 @@
         <v>44607</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -69832,7 +69832,7 @@
         <v>44638</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -69910,7 +69910,7 @@
         <v>45020</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -69988,7 +69988,7 @@
         <v>45386</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70066,7 +70066,7 @@
         <v>45638</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -70144,7 +70144,7 @@
         <v>45250</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -70222,7 +70222,7 @@
         <v>45021</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -70300,7 +70300,7 @@
         <v>44943</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -70378,7 +70378,7 @@
         <v>45755</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -70451,7 +70451,7 @@
         <v>45834</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -70529,7 +70529,7 @@
         <v>45755</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -70602,7 +70602,7 @@
         <v>46168</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>46247</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -70753,7 +70753,7 @@
         <v>46309</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -70831,7 +70831,7 @@
         <v>46316</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
